--- a/docs/rpg/RPG_밸런스기획서.xlsx
+++ b/docs/rpg/RPG_밸런스기획서.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="맑은 고딕"/>
       <family val="2"/>
@@ -151,6 +151,7 @@
       <b val="1"/>
       <sz val="11"/>
     </font>
+    <font/>
   </fonts>
   <fills count="12">
     <fill>
@@ -210,7 +211,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -293,11 +294,12 @@
       </bottom>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -349,6 +351,8 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
@@ -907,11 +911,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H177"/>
+  <dimension ref="A1:Z177"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col width="20" customWidth="1" style="24" min="1" max="1"/>
     <col width="13" customWidth="1" style="24" min="2" max="8"/>
+    <col width="20" customWidth="1" style="24" min="4" max="4"/>
+    <col width="13" customWidth="1" style="24" min="5" max="5"/>
+    <col width="20" customWidth="1" style="24" min="6" max="6"/>
+    <col width="20" customWidth="1" style="24" min="7" max="7"/>
+    <col width="13" customWidth="1" style="24" min="8" max="8"/>
+    <col width="20" customWidth="1" style="24" min="11" max="11"/>
+    <col width="13" customWidth="1" style="24" min="12" max="12"/>
+    <col width="20" customWidth="1" style="24" min="19" max="19"/>
+    <col width="13" customWidth="1" style="24" min="20" max="20"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1" s="24">
@@ -1029,11 +1042,11 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>B26+B27*($A$5/$B$5)+B25*($A$5/$C$5)+B30*$D$5+B29*$E$5</f>
+        <f>G15+H16*($A$5/$B$5)+G14*($A$5/$C$5)+G19*$D$5+G18*$E$5</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>C26+C27*($A$5/$B$5)+C25*($A$5/$C$5)+C30*$D$5+C29*$E$5</f>
+        <f>H15+I16*($A$5/$B$5)+H14*($A$5/$C$5)+H19*$D$5+H18*$E$5</f>
         <v/>
       </c>
       <c r="D9" s="16">
@@ -1052,11 +1065,11 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>B37+B38*($A$5/$B$5)+B36*($A$5/$C$5)+B41*$D$5+B40*$E$5</f>
+        <f>L15+M16*($A$5/$B$5)+L14*($A$5/$C$5)+L19*$D$5+L18*$E$5</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>C37+C38*($A$5/$B$5)+C36*($A$5/$C$5)+C41*$D$5+C40*$E$5</f>
+        <f>M15+N16*($A$5/$B$5)+M14*($A$5/$C$5)+M19*$D$5+M18*$E$5</f>
         <v/>
       </c>
       <c r="D10" s="16">
@@ -1081,6 +1094,16 @@
           <t>[탱커 (가칭)] 레벨 성장 곡선 앵커값 (직접 결정)</t>
         </is>
       </c>
+      <c r="F12" s="22" t="inlineStr">
+        <is>
+          <t>[물리딜러 (가칭)] 레벨 성장 곡선 앵커값 (직접 결정)</t>
+        </is>
+      </c>
+      <c r="K12" s="22" t="inlineStr">
+        <is>
+          <t>[마법딜러·힐러 (가칭)] 레벨 성장 곡선 앵커값 (직접 결정)</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="54" customHeight="1" s="24">
       <c r="A13" s="14" t="inlineStr">
@@ -1103,6 +1126,46 @@
           <t>곡선계수 k (0=선형, 1=완전 3차)</t>
         </is>
       </c>
+      <c r="F13" s="19" t="inlineStr">
+        <is>
+          <t>스탯</t>
+        </is>
+      </c>
+      <c r="G13" s="19" t="inlineStr">
+        <is>
+          <t>Lv1 값</t>
+        </is>
+      </c>
+      <c r="H13" s="19" t="inlineStr">
+        <is>
+          <t>Lv30 값</t>
+        </is>
+      </c>
+      <c r="I13" s="19" t="inlineStr">
+        <is>
+          <t>곡선계수 k (0=선형, 1=완전 3차)</t>
+        </is>
+      </c>
+      <c r="K13" s="19" t="inlineStr">
+        <is>
+          <t>스탯</t>
+        </is>
+      </c>
+      <c r="L13" s="19" t="inlineStr">
+        <is>
+          <t>Lv1 값</t>
+        </is>
+      </c>
+      <c r="M13" s="19" t="inlineStr">
+        <is>
+          <t>Lv30 값</t>
+        </is>
+      </c>
+      <c r="N13" s="19" t="inlineStr">
+        <is>
+          <t>곡선계수 k (0=선형, 1=완전 3차)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="16" t="inlineStr">
@@ -1119,6 +1182,34 @@
       <c r="D14" s="15" t="n">
         <v>0</v>
       </c>
+      <c r="F14" s="33" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="H14" s="21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="I14" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="33" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="L14" s="21" t="n">
+        <v>50</v>
+      </c>
+      <c r="M14" s="21" t="n">
+        <v>840</v>
+      </c>
+      <c r="N14" s="21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="16" t="inlineStr">
@@ -1135,6 +1226,34 @@
       <c r="D15" s="15" t="n">
         <v>0</v>
       </c>
+      <c r="F15" s="33" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>55</v>
+      </c>
+      <c r="H15" s="21" t="n">
+        <v>500</v>
+      </c>
+      <c r="I15" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="33" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="L15" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="M15" s="21" t="n">
+        <v>110</v>
+      </c>
+      <c r="N15" s="21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="16" t="inlineStr">
@@ -1151,6 +1270,34 @@
       <c r="D16" s="15" t="n">
         <v>0</v>
       </c>
+      <c r="F16" s="33" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="G16" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="H16" s="21" t="n">
+        <v>300</v>
+      </c>
+      <c r="I16" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="33" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="L16" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="M16" s="21" t="n">
+        <v>300</v>
+      </c>
+      <c r="N16" s="21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="16" t="inlineStr">
@@ -1167,6 +1314,34 @@
       <c r="D17" s="15" t="n">
         <v>0</v>
       </c>
+      <c r="F17" s="33" t="inlineStr">
+        <is>
+          <t>속도</t>
+        </is>
+      </c>
+      <c r="G17" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="H17" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="I17" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="33" t="inlineStr">
+        <is>
+          <t>속도</t>
+        </is>
+      </c>
+      <c r="L17" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="M17" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="N17" s="21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="16" t="inlineStr">
@@ -1183,6 +1358,34 @@
       <c r="D18" s="15" t="n">
         <v>0</v>
       </c>
+      <c r="F18" s="33" t="inlineStr">
+        <is>
+          <t>힘</t>
+        </is>
+      </c>
+      <c r="G18" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="H18" s="21" t="n">
+        <v>150</v>
+      </c>
+      <c r="I18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="33" t="inlineStr">
+        <is>
+          <t>힘</t>
+        </is>
+      </c>
+      <c r="L18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="16" t="inlineStr">
@@ -1199,6 +1402,34 @@
       <c r="D19" s="15" t="n">
         <v>0</v>
       </c>
+      <c r="F19" s="33" t="inlineStr">
+        <is>
+          <t>지력</t>
+        </is>
+      </c>
+      <c r="G19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="33" t="inlineStr">
+        <is>
+          <t>지력</t>
+        </is>
+      </c>
+      <c r="L19" s="21" t="n">
+        <v>20</v>
+      </c>
+      <c r="M19" s="21" t="n">
+        <v>200</v>
+      </c>
+      <c r="N19" s="21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="16" t="inlineStr">
@@ -1215,288 +1446,154 @@
       <c r="D20" s="15" t="n">
         <v>0</v>
       </c>
+      <c r="F20" s="33" t="inlineStr">
+        <is>
+          <t>치료효율</t>
+        </is>
+      </c>
+      <c r="G20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="33" t="inlineStr">
+        <is>
+          <t>치료효율</t>
+        </is>
+      </c>
+      <c r="L20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="28" t="inlineStr">
-        <is>
-          <t>[물리딜러 (가칭)] 레벨 성장 곡선 앵커값 (직접 결정)</t>
-        </is>
-      </c>
+      <c r="A23" s="34" t="n"/>
+      <c r="B23" s="34" t="n"/>
+      <c r="C23" s="34" t="n"/>
+      <c r="D23" s="34" t="n"/>
     </row>
     <row r="24" ht="54" customHeight="1" s="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>스탯</t>
-        </is>
-      </c>
-      <c r="B24" s="14" t="inlineStr">
-        <is>
-          <t>Lv1 값</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="inlineStr">
-        <is>
-          <t>Lv30 값</t>
-        </is>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>곡선계수 k (0=선형, 1=완전 3차)</t>
-        </is>
-      </c>
+      <c r="A24" s="34" t="n"/>
+      <c r="B24" s="34" t="n"/>
+      <c r="C24" s="34" t="n"/>
+      <c r="D24" s="34" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="n">
-        <v>50</v>
-      </c>
-      <c r="C25" s="15" t="n">
-        <v>1000</v>
-      </c>
-      <c r="D25" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="A25" s="34" t="n"/>
+      <c r="B25" s="34" t="n"/>
+      <c r="C25" s="34" t="n"/>
+      <c r="D25" s="34" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="16" t="inlineStr">
-        <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="n">
-        <v>55</v>
-      </c>
-      <c r="C26" s="15" t="n">
-        <v>500</v>
-      </c>
-      <c r="D26" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="A26" s="34" t="n"/>
+      <c r="B26" s="34" t="n"/>
+      <c r="C26" s="34" t="n"/>
+      <c r="D26" s="34" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="16" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="C27" s="15" t="n">
-        <v>300</v>
-      </c>
-      <c r="D27" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="A27" s="34" t="n"/>
+      <c r="B27" s="34" t="n"/>
+      <c r="C27" s="34" t="n"/>
+      <c r="D27" s="34" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>속도</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="C28" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="D28" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="A28" s="34" t="n"/>
+      <c r="B28" s="34" t="n"/>
+      <c r="C28" s="34" t="n"/>
+      <c r="D28" s="34" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>힘</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="C29" s="15" t="n">
-        <v>150</v>
-      </c>
-      <c r="D29" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="A29" s="34" t="n"/>
+      <c r="B29" s="34" t="n"/>
+      <c r="C29" s="34" t="n"/>
+      <c r="D29" s="34" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>지력</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D30" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="A30" s="34" t="n"/>
+      <c r="B30" s="34" t="n"/>
+      <c r="C30" s="34" t="n"/>
+      <c r="D30" s="34" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="16" t="inlineStr">
-        <is>
-          <t>치료효율</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="A31" s="34" t="n"/>
+      <c r="B31" s="34" t="n"/>
+      <c r="C31" s="34" t="n"/>
+      <c r="D31" s="34" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="34" t="n"/>
+      <c r="B32" s="34" t="n"/>
+      <c r="C32" s="34" t="n"/>
+      <c r="D32" s="34" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="34" t="n"/>
+      <c r="B33" s="34" t="n"/>
+      <c r="C33" s="34" t="n"/>
+      <c r="D33" s="34" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="28" t="inlineStr">
-        <is>
-          <t>[마법딜러·힐러 (가칭)] 레벨 성장 곡선 앵커값 (직접 결정)</t>
-        </is>
-      </c>
+      <c r="A34" s="34" t="n"/>
+      <c r="B34" s="34" t="n"/>
+      <c r="C34" s="34" t="n"/>
+      <c r="D34" s="34" t="n"/>
     </row>
     <row r="35" ht="54" customHeight="1" s="24">
-      <c r="A35" s="14" t="inlineStr">
-        <is>
-          <t>스탯</t>
-        </is>
-      </c>
-      <c r="B35" s="14" t="inlineStr">
-        <is>
-          <t>Lv1 값</t>
-        </is>
-      </c>
-      <c r="C35" s="14" t="inlineStr">
-        <is>
-          <t>Lv30 값</t>
-        </is>
-      </c>
-      <c r="D35" s="14" t="inlineStr">
-        <is>
-          <t>곡선계수 k (0=선형, 1=완전 3차)</t>
-        </is>
-      </c>
+      <c r="A35" s="34" t="n"/>
+      <c r="B35" s="34" t="n"/>
+      <c r="C35" s="34" t="n"/>
+      <c r="D35" s="34" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="16" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="B36" s="15" t="n">
-        <v>50</v>
-      </c>
-      <c r="C36" s="15" t="n">
-        <v>840</v>
-      </c>
-      <c r="D36" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="A36" s="34" t="n"/>
+      <c r="B36" s="34" t="n"/>
+      <c r="C36" s="34" t="n"/>
+      <c r="D36" s="34" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="16" t="inlineStr">
-        <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="B37" s="15" t="n">
-        <v>10</v>
-      </c>
-      <c r="C37" s="15" t="n">
-        <v>110</v>
-      </c>
-      <c r="D37" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="A37" s="34" t="n"/>
+      <c r="B37" s="34" t="n"/>
+      <c r="C37" s="34" t="n"/>
+      <c r="D37" s="34" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="16" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="B38" s="15" t="n">
-        <v>30</v>
-      </c>
-      <c r="C38" s="15" t="n">
-        <v>300</v>
-      </c>
-      <c r="D38" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="A38" s="34" t="n"/>
+      <c r="B38" s="34" t="n"/>
+      <c r="C38" s="34" t="n"/>
+      <c r="D38" s="34" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>속도</t>
-        </is>
-      </c>
-      <c r="B39" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="C39" s="15" t="n">
-        <v>15</v>
-      </c>
-      <c r="D39" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="A39" s="34" t="n"/>
+      <c r="B39" s="34" t="n"/>
+      <c r="C39" s="34" t="n"/>
+      <c r="D39" s="34" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="16" t="inlineStr">
-        <is>
-          <t>힘</t>
-        </is>
-      </c>
-      <c r="B40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C40" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="A40" s="34" t="n"/>
+      <c r="B40" s="34" t="n"/>
+      <c r="C40" s="34" t="n"/>
+      <c r="D40" s="34" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="16" t="inlineStr">
-        <is>
-          <t>지력</t>
-        </is>
-      </c>
-      <c r="B41" s="15" t="n">
-        <v>20</v>
-      </c>
-      <c r="C41" s="15" t="n">
-        <v>200</v>
-      </c>
-      <c r="D41" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="A41" s="34" t="n"/>
+      <c r="B41" s="34" t="n"/>
+      <c r="C41" s="34" t="n"/>
+      <c r="D41" s="34" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="16" t="inlineStr">
-        <is>
-          <t>치료효율</t>
-        </is>
-      </c>
-      <c r="B42" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C42" s="15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="A42" s="34" t="n"/>
+      <c r="B42" s="34" t="n"/>
+      <c r="C42" s="34" t="n"/>
+      <c r="D42" s="34" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="28" t="inlineStr">
@@ -1504,6 +1601,16 @@
           <t>[탱커 (가칭)] 종족 고정 스탯 (2단계, 레벨 무관 — 직접 결정)</t>
         </is>
       </c>
+      <c r="D45" s="22" t="inlineStr">
+        <is>
+          <t>[물리딜러 (가칭)] 종족 고정 스탯 (2단계, 레벨 무관, 직접 결정)</t>
+        </is>
+      </c>
+      <c r="G45" s="22" t="inlineStr">
+        <is>
+          <t>[마법딜러·힐러 (가칭)] 종족 고정 스탯 (2단계, 레벨 무관, 직접 결정)</t>
+        </is>
+      </c>
     </row>
     <row r="46" ht="18" customHeight="1" s="24">
       <c r="A46" s="14" t="inlineStr">
@@ -1516,6 +1623,26 @@
           <t>값 (%)</t>
         </is>
       </c>
+      <c r="D46" s="19" t="inlineStr">
+        <is>
+          <t>스탯</t>
+        </is>
+      </c>
+      <c r="E46" s="19" t="inlineStr">
+        <is>
+          <t>값 (%)</t>
+        </is>
+      </c>
+      <c r="G46" s="19" t="inlineStr">
+        <is>
+          <t>스탯</t>
+        </is>
+      </c>
+      <c r="H46" s="19" t="inlineStr">
+        <is>
+          <t>값 (%)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
@@ -1526,6 +1653,22 @@
       <c r="B47" s="15" t="n">
         <v>15</v>
       </c>
+      <c r="D47" s="33" t="inlineStr">
+        <is>
+          <t>크리티컬확률%</t>
+        </is>
+      </c>
+      <c r="E47" s="21" t="n">
+        <v>25</v>
+      </c>
+      <c r="G47" s="33" t="inlineStr">
+        <is>
+          <t>크리티컬확률%</t>
+        </is>
+      </c>
+      <c r="H47" s="21" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
@@ -1536,6 +1679,22 @@
       <c r="B48" s="15" t="n">
         <v>200</v>
       </c>
+      <c r="D48" s="33" t="inlineStr">
+        <is>
+          <t>크리티컬피해%</t>
+        </is>
+      </c>
+      <c r="E48" s="21" t="n">
+        <v>200</v>
+      </c>
+      <c r="G48" s="33" t="inlineStr">
+        <is>
+          <t>크리티컬피해%</t>
+        </is>
+      </c>
+      <c r="H48" s="21" t="n">
+        <v>200</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
@@ -1546,6 +1705,22 @@
       <c r="B49" s="15" t="n">
         <v>20</v>
       </c>
+      <c r="D49" s="33" t="inlineStr">
+        <is>
+          <t>물리피해%</t>
+        </is>
+      </c>
+      <c r="E49" s="21" t="n">
+        <v>40</v>
+      </c>
+      <c r="G49" s="33" t="inlineStr">
+        <is>
+          <t>물리피해%</t>
+        </is>
+      </c>
+      <c r="H49" s="21" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
@@ -1556,6 +1731,22 @@
       <c r="B50" s="15" t="n">
         <v>0</v>
       </c>
+      <c r="D50" s="33" t="inlineStr">
+        <is>
+          <t>마법피해%</t>
+        </is>
+      </c>
+      <c r="E50" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G50" s="33" t="inlineStr">
+        <is>
+          <t>마법피해%</t>
+        </is>
+      </c>
+      <c r="H50" s="21" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
@@ -1566,6 +1757,22 @@
       <c r="B51" s="15" t="n">
         <v>30</v>
       </c>
+      <c r="D51" s="33" t="inlineStr">
+        <is>
+          <t>물리저항%</t>
+        </is>
+      </c>
+      <c r="E51" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G51" s="33" t="inlineStr">
+        <is>
+          <t>물리저항%</t>
+        </is>
+      </c>
+      <c r="H51" s="21" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
@@ -1576,6 +1783,22 @@
       <c r="B52" s="15" t="n">
         <v>30</v>
       </c>
+      <c r="D52" s="33" t="inlineStr">
+        <is>
+          <t>마법저항%</t>
+        </is>
+      </c>
+      <c r="E52" s="21" t="n">
+        <v>10</v>
+      </c>
+      <c r="G52" s="33" t="inlineStr">
+        <is>
+          <t>마법저항%</t>
+        </is>
+      </c>
+      <c r="H52" s="21" t="n">
+        <v>10</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
@@ -1586,184 +1809,102 @@
       <c r="B53" s="15" t="n">
         <v>10</v>
       </c>
+      <c r="D53" s="33" t="inlineStr">
+        <is>
+          <t>회피%</t>
+        </is>
+      </c>
+      <c r="E53" s="21" t="n">
+        <v>30</v>
+      </c>
+      <c r="G53" s="33" t="inlineStr">
+        <is>
+          <t>회피%</t>
+        </is>
+      </c>
+      <c r="H53" s="21" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="56">
-      <c r="A56" s="28" t="inlineStr">
-        <is>
-          <t>[물리딜러 (가칭)] 종족 고정 스탯 (2단계, 레벨 무관 — 직접 결정)</t>
-        </is>
-      </c>
+      <c r="A56" s="34" t="n"/>
+      <c r="B56" s="34" t="n"/>
     </row>
     <row r="57" ht="18" customHeight="1" s="24">
-      <c r="A57" s="14" t="inlineStr">
-        <is>
-          <t>스탯</t>
-        </is>
-      </c>
-      <c r="B57" s="14" t="inlineStr">
-        <is>
-          <t>값 (%)</t>
-        </is>
-      </c>
+      <c r="A57" s="34" t="n"/>
+      <c r="B57" s="34" t="n"/>
     </row>
     <row r="58">
-      <c r="A58" s="16" t="inlineStr">
-        <is>
-          <t>크리티컬확률%</t>
-        </is>
-      </c>
-      <c r="B58" s="15" t="n">
-        <v>25</v>
-      </c>
+      <c r="A58" s="34" t="n"/>
+      <c r="B58" s="34" t="n"/>
     </row>
     <row r="59">
-      <c r="A59" s="16" t="inlineStr">
-        <is>
-          <t>크리티컬피해%</t>
-        </is>
-      </c>
-      <c r="B59" s="15" t="n">
-        <v>200</v>
-      </c>
+      <c r="A59" s="34" t="n"/>
+      <c r="B59" s="34" t="n"/>
     </row>
     <row r="60">
-      <c r="A60" s="16" t="inlineStr">
-        <is>
-          <t>물리피해%</t>
-        </is>
-      </c>
-      <c r="B60" s="15" t="n">
-        <v>40</v>
-      </c>
+      <c r="A60" s="34" t="n"/>
+      <c r="B60" s="34" t="n"/>
     </row>
     <row r="61">
-      <c r="A61" s="16" t="inlineStr">
-        <is>
-          <t>마법피해%</t>
-        </is>
-      </c>
-      <c r="B61" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="A61" s="34" t="n"/>
+      <c r="B61" s="34" t="n"/>
     </row>
     <row r="62">
-      <c r="A62" s="16" t="inlineStr">
-        <is>
-          <t>물리저항%</t>
-        </is>
-      </c>
-      <c r="B62" s="15" t="n">
-        <v>10</v>
-      </c>
+      <c r="A62" s="34" t="n"/>
+      <c r="B62" s="34" t="n"/>
     </row>
     <row r="63">
-      <c r="A63" s="16" t="inlineStr">
-        <is>
-          <t>마법저항%</t>
-        </is>
-      </c>
-      <c r="B63" s="15" t="n">
-        <v>10</v>
-      </c>
+      <c r="A63" s="34" t="n"/>
+      <c r="B63" s="34" t="n"/>
     </row>
     <row r="64">
-      <c r="A64" s="16" t="inlineStr">
-        <is>
-          <t>회피%</t>
-        </is>
-      </c>
-      <c r="B64" s="15" t="n">
-        <v>30</v>
-      </c>
+      <c r="A64" s="34" t="n"/>
+      <c r="B64" s="34" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="34" t="n"/>
+      <c r="B65" s="34" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="34" t="n"/>
+      <c r="B66" s="34" t="n"/>
     </row>
     <row r="67">
-      <c r="A67" s="28" t="inlineStr">
-        <is>
-          <t>[마법딜러·힐러 (가칭)] 종족 고정 스탯 (2단계, 레벨 무관 — 직접 결정)</t>
-        </is>
-      </c>
+      <c r="A67" s="34" t="n"/>
+      <c r="B67" s="34" t="n"/>
     </row>
     <row r="68" ht="18" customHeight="1" s="24">
-      <c r="A68" s="14" t="inlineStr">
-        <is>
-          <t>스탯</t>
-        </is>
-      </c>
-      <c r="B68" s="14" t="inlineStr">
-        <is>
-          <t>값 (%)</t>
-        </is>
-      </c>
+      <c r="A68" s="34" t="n"/>
+      <c r="B68" s="34" t="n"/>
     </row>
     <row r="69">
-      <c r="A69" s="16" t="inlineStr">
-        <is>
-          <t>크리티컬확률%</t>
-        </is>
-      </c>
-      <c r="B69" s="15" t="n">
-        <v>20</v>
-      </c>
+      <c r="A69" s="34" t="n"/>
+      <c r="B69" s="34" t="n"/>
     </row>
     <row r="70">
-      <c r="A70" s="16" t="inlineStr">
-        <is>
-          <t>크리티컬피해%</t>
-        </is>
-      </c>
-      <c r="B70" s="15" t="n">
-        <v>200</v>
-      </c>
+      <c r="A70" s="34" t="n"/>
+      <c r="B70" s="34" t="n"/>
     </row>
     <row r="71">
-      <c r="A71" s="16" t="inlineStr">
-        <is>
-          <t>물리피해%</t>
-        </is>
-      </c>
-      <c r="B71" s="15" t="n">
-        <v>0</v>
-      </c>
+      <c r="A71" s="34" t="n"/>
+      <c r="B71" s="34" t="n"/>
     </row>
     <row r="72">
-      <c r="A72" s="16" t="inlineStr">
-        <is>
-          <t>마법피해%</t>
-        </is>
-      </c>
-      <c r="B72" s="15" t="n">
-        <v>30</v>
-      </c>
+      <c r="A72" s="34" t="n"/>
+      <c r="B72" s="34" t="n"/>
     </row>
     <row r="73">
-      <c r="A73" s="16" t="inlineStr">
-        <is>
-          <t>물리저항%</t>
-        </is>
-      </c>
-      <c r="B73" s="15" t="n">
-        <v>10</v>
-      </c>
+      <c r="A73" s="34" t="n"/>
+      <c r="B73" s="34" t="n"/>
     </row>
     <row r="74">
-      <c r="A74" s="16" t="inlineStr">
-        <is>
-          <t>마법저항%</t>
-        </is>
-      </c>
-      <c r="B74" s="15" t="n">
-        <v>10</v>
-      </c>
+      <c r="A74" s="34" t="n"/>
+      <c r="B74" s="34" t="n"/>
     </row>
     <row r="75">
-      <c r="A75" s="16" t="inlineStr">
-        <is>
-          <t>회피%</t>
-        </is>
-      </c>
-      <c r="B75" s="15" t="n">
-        <v>20</v>
-      </c>
+      <c r="A75" s="34" t="n"/>
+      <c r="B75" s="34" t="n"/>
     </row>
     <row r="78">
       <c r="A78" s="28" t="inlineStr">
@@ -1771,6 +1912,16 @@
           <t>[탱커 (가칭)] 레벨 1~30 스탯 (자동 계산)</t>
         </is>
       </c>
+      <c r="J78" s="22" t="inlineStr">
+        <is>
+          <t>[물리딜러 (가칭)] 레벨 1~30 스탯 (자동 계산)</t>
+        </is>
+      </c>
+      <c r="S78" s="22" t="inlineStr">
+        <is>
+          <t>[마법딜러·힐러 (가칭)] 레벨 1~30 스탯 (자동 계산)</t>
+        </is>
+      </c>
     </row>
     <row r="79" ht="18" customHeight="1" s="24">
       <c r="A79" s="14" t="inlineStr">
@@ -1809,6 +1960,86 @@
         </is>
       </c>
       <c r="H79" s="14" t="inlineStr">
+        <is>
+          <t>치료효율</t>
+        </is>
+      </c>
+      <c r="J79" s="19" t="inlineStr">
+        <is>
+          <t>레벨</t>
+        </is>
+      </c>
+      <c r="K79" s="19" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="L79" s="19" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="M79" s="19" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="N79" s="19" t="inlineStr">
+        <is>
+          <t>속도</t>
+        </is>
+      </c>
+      <c r="O79" s="19" t="inlineStr">
+        <is>
+          <t>힘</t>
+        </is>
+      </c>
+      <c r="P79" s="19" t="inlineStr">
+        <is>
+          <t>지력</t>
+        </is>
+      </c>
+      <c r="Q79" s="19" t="inlineStr">
+        <is>
+          <t>치료효율</t>
+        </is>
+      </c>
+      <c r="S79" s="19" t="inlineStr">
+        <is>
+          <t>레벨</t>
+        </is>
+      </c>
+      <c r="T79" s="19" t="inlineStr">
+        <is>
+          <t>HP</t>
+        </is>
+      </c>
+      <c r="U79" s="19" t="inlineStr">
+        <is>
+          <t>ATK</t>
+        </is>
+      </c>
+      <c r="V79" s="19" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="W79" s="19" t="inlineStr">
+        <is>
+          <t>속도</t>
+        </is>
+      </c>
+      <c r="X79" s="19" t="inlineStr">
+        <is>
+          <t>힘</t>
+        </is>
+      </c>
+      <c r="Y79" s="19" t="inlineStr">
+        <is>
+          <t>지력</t>
+        </is>
+      </c>
+      <c r="Z79" s="19" t="inlineStr">
         <is>
           <t>치료효율</t>
         </is>
@@ -1846,6 +2077,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0+$D$20*0^3),0)</f>
         <v/>
       </c>
+      <c r="J80" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="K80" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.0+$I$14*0.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="L80" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.0+$I$15*0.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="M80" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.0+$I$16*0.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="N80" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.0+$I$17*0.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="O80" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.0+$I$18*0.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="P80" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.0+$I$19*0.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q80" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.0+$I$20*0.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="S80" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T80" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.0+$N$14*0.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="U80" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.0+$N$15*0.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="V80" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.0+$N$16*0.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="W80" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.0+$N$17*0.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="X80" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.0+$N$18*0.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y80" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.0+$N$19*0.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z80" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.0+$N$20*0.0^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="16" t="n">
@@ -1879,6 +2172,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.0344827586206896+$D$20*0.0344827586206896^3),0)</f>
         <v/>
       </c>
+      <c r="J81" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="K81" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.034482758620689655+$I$14*0.034482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="L81" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.034482758620689655+$I$15*0.034482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="M81" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.034482758620689655+$I$16*0.034482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="N81" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.034482758620689655+$I$17*0.034482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="O81" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.034482758620689655+$I$18*0.034482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="P81" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.034482758620689655+$I$19*0.034482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q81" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.034482758620689655+$I$20*0.034482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="S81" s="33" t="n">
+        <v>2</v>
+      </c>
+      <c r="T81" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.034482758620689655+$N$14*0.034482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="U81" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.034482758620689655+$N$15*0.034482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="V81" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.034482758620689655+$N$16*0.034482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="W81" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.034482758620689655+$N$17*0.034482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="X81" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.034482758620689655+$N$18*0.034482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y81" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.034482758620689655+$N$19*0.034482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z81" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.034482758620689655+$N$20*0.034482758620689655^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="16" t="n">
@@ -1912,6 +2267,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.0689655172413793+$D$20*0.0689655172413793^3),0)</f>
         <v/>
       </c>
+      <c r="J82" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="K82" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.06896551724137931+$I$14*0.06896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="L82" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.06896551724137931+$I$15*0.06896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="M82" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.06896551724137931+$I$16*0.06896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="N82" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.06896551724137931+$I$17*0.06896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="O82" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.06896551724137931+$I$18*0.06896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="P82" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.06896551724137931+$I$19*0.06896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q82" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.06896551724137931+$I$20*0.06896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="S82" s="33" t="n">
+        <v>3</v>
+      </c>
+      <c r="T82" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.06896551724137931+$N$14*0.06896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="U82" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.06896551724137931+$N$15*0.06896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="V82" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.06896551724137931+$N$16*0.06896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="W82" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.06896551724137931+$N$17*0.06896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="X82" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.06896551724137931+$N$18*0.06896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y82" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.06896551724137931+$N$19*0.06896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z82" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.06896551724137931+$N$20*0.06896551724137931^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="16" t="n">
@@ -1945,6 +2362,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.103448275862068+$D$20*0.103448275862068^3),0)</f>
         <v/>
       </c>
+      <c r="J83" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="K83" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.10344827586206896+$I$14*0.10344827586206896^3),0)</f>
+        <v/>
+      </c>
+      <c r="L83" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.10344827586206896+$I$15*0.10344827586206896^3),0)</f>
+        <v/>
+      </c>
+      <c r="M83" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.10344827586206896+$I$16*0.10344827586206896^3),0)</f>
+        <v/>
+      </c>
+      <c r="N83" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.10344827586206896+$I$17*0.10344827586206896^3),0)</f>
+        <v/>
+      </c>
+      <c r="O83" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.10344827586206896+$I$18*0.10344827586206896^3),0)</f>
+        <v/>
+      </c>
+      <c r="P83" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.10344827586206896+$I$19*0.10344827586206896^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q83" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.10344827586206896+$I$20*0.10344827586206896^3),0)</f>
+        <v/>
+      </c>
+      <c r="S83" s="33" t="n">
+        <v>4</v>
+      </c>
+      <c r="T83" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.10344827586206896+$N$14*0.10344827586206896^3),0)</f>
+        <v/>
+      </c>
+      <c r="U83" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.10344827586206896+$N$15*0.10344827586206896^3),0)</f>
+        <v/>
+      </c>
+      <c r="V83" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.10344827586206896+$N$16*0.10344827586206896^3),0)</f>
+        <v/>
+      </c>
+      <c r="W83" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.10344827586206896+$N$17*0.10344827586206896^3),0)</f>
+        <v/>
+      </c>
+      <c r="X83" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.10344827586206896+$N$18*0.10344827586206896^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y83" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.10344827586206896+$N$19*0.10344827586206896^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z83" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.10344827586206896+$N$20*0.10344827586206896^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="16" t="n">
@@ -1978,6 +2457,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.137931034482758+$D$20*0.137931034482758^3),0)</f>
         <v/>
       </c>
+      <c r="J84" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="K84" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.13793103448275862+$I$14*0.13793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="L84" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.13793103448275862+$I$15*0.13793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="M84" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.13793103448275862+$I$16*0.13793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="N84" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.13793103448275862+$I$17*0.13793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="O84" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.13793103448275862+$I$18*0.13793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="P84" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.13793103448275862+$I$19*0.13793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q84" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.13793103448275862+$I$20*0.13793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="S84" s="33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T84" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.13793103448275862+$N$14*0.13793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="U84" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.13793103448275862+$N$15*0.13793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="V84" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.13793103448275862+$N$16*0.13793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="W84" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.13793103448275862+$N$17*0.13793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="X84" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.13793103448275862+$N$18*0.13793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y84" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.13793103448275862+$N$19*0.13793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z84" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.13793103448275862+$N$20*0.13793103448275862^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="16" t="n">
@@ -2011,6 +2552,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.172413793103448+$D$20*0.172413793103448^3),0)</f>
         <v/>
       </c>
+      <c r="J85" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="K85" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.1724137931034483+$I$14*0.1724137931034483^3),0)</f>
+        <v/>
+      </c>
+      <c r="L85" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.1724137931034483+$I$15*0.1724137931034483^3),0)</f>
+        <v/>
+      </c>
+      <c r="M85" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.1724137931034483+$I$16*0.1724137931034483^3),0)</f>
+        <v/>
+      </c>
+      <c r="N85" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.1724137931034483+$I$17*0.1724137931034483^3),0)</f>
+        <v/>
+      </c>
+      <c r="O85" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.1724137931034483+$I$18*0.1724137931034483^3),0)</f>
+        <v/>
+      </c>
+      <c r="P85" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.1724137931034483+$I$19*0.1724137931034483^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q85" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.1724137931034483+$I$20*0.1724137931034483^3),0)</f>
+        <v/>
+      </c>
+      <c r="S85" s="33" t="n">
+        <v>6</v>
+      </c>
+      <c r="T85" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.1724137931034483+$N$14*0.1724137931034483^3),0)</f>
+        <v/>
+      </c>
+      <c r="U85" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.1724137931034483+$N$15*0.1724137931034483^3),0)</f>
+        <v/>
+      </c>
+      <c r="V85" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.1724137931034483+$N$16*0.1724137931034483^3),0)</f>
+        <v/>
+      </c>
+      <c r="W85" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.1724137931034483+$N$17*0.1724137931034483^3),0)</f>
+        <v/>
+      </c>
+      <c r="X85" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.1724137931034483+$N$18*0.1724137931034483^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y85" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.1724137931034483+$N$19*0.1724137931034483^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z85" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.1724137931034483+$N$20*0.1724137931034483^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="16" t="n">
@@ -2044,6 +2647,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.206896551724137+$D$20*0.206896551724137^3),0)</f>
         <v/>
       </c>
+      <c r="J86" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="K86" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.20689655172413793+$I$14*0.20689655172413793^3),0)</f>
+        <v/>
+      </c>
+      <c r="L86" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.20689655172413793+$I$15*0.20689655172413793^3),0)</f>
+        <v/>
+      </c>
+      <c r="M86" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.20689655172413793+$I$16*0.20689655172413793^3),0)</f>
+        <v/>
+      </c>
+      <c r="N86" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.20689655172413793+$I$17*0.20689655172413793^3),0)</f>
+        <v/>
+      </c>
+      <c r="O86" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.20689655172413793+$I$18*0.20689655172413793^3),0)</f>
+        <v/>
+      </c>
+      <c r="P86" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.20689655172413793+$I$19*0.20689655172413793^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q86" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.20689655172413793+$I$20*0.20689655172413793^3),0)</f>
+        <v/>
+      </c>
+      <c r="S86" s="33" t="n">
+        <v>7</v>
+      </c>
+      <c r="T86" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.20689655172413793+$N$14*0.20689655172413793^3),0)</f>
+        <v/>
+      </c>
+      <c r="U86" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.20689655172413793+$N$15*0.20689655172413793^3),0)</f>
+        <v/>
+      </c>
+      <c r="V86" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.20689655172413793+$N$16*0.20689655172413793^3),0)</f>
+        <v/>
+      </c>
+      <c r="W86" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.20689655172413793+$N$17*0.20689655172413793^3),0)</f>
+        <v/>
+      </c>
+      <c r="X86" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.20689655172413793+$N$18*0.20689655172413793^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y86" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.20689655172413793+$N$19*0.20689655172413793^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z86" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.20689655172413793+$N$20*0.20689655172413793^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="16" t="n">
@@ -2077,6 +2742,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.241379310344827+$D$20*0.241379310344827^3),0)</f>
         <v/>
       </c>
+      <c r="J87" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="K87" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.2413793103448276+$I$14*0.2413793103448276^3),0)</f>
+        <v/>
+      </c>
+      <c r="L87" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.2413793103448276+$I$15*0.2413793103448276^3),0)</f>
+        <v/>
+      </c>
+      <c r="M87" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.2413793103448276+$I$16*0.2413793103448276^3),0)</f>
+        <v/>
+      </c>
+      <c r="N87" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.2413793103448276+$I$17*0.2413793103448276^3),0)</f>
+        <v/>
+      </c>
+      <c r="O87" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.2413793103448276+$I$18*0.2413793103448276^3),0)</f>
+        <v/>
+      </c>
+      <c r="P87" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.2413793103448276+$I$19*0.2413793103448276^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q87" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.2413793103448276+$I$20*0.2413793103448276^3),0)</f>
+        <v/>
+      </c>
+      <c r="S87" s="33" t="n">
+        <v>8</v>
+      </c>
+      <c r="T87" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.2413793103448276+$N$14*0.2413793103448276^3),0)</f>
+        <v/>
+      </c>
+      <c r="U87" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.2413793103448276+$N$15*0.2413793103448276^3),0)</f>
+        <v/>
+      </c>
+      <c r="V87" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.2413793103448276+$N$16*0.2413793103448276^3),0)</f>
+        <v/>
+      </c>
+      <c r="W87" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.2413793103448276+$N$17*0.2413793103448276^3),0)</f>
+        <v/>
+      </c>
+      <c r="X87" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.2413793103448276+$N$18*0.2413793103448276^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y87" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.2413793103448276+$N$19*0.2413793103448276^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z87" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.2413793103448276+$N$20*0.2413793103448276^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="16" t="n">
@@ -2110,6 +2837,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.275862068965517+$D$20*0.275862068965517^3),0)</f>
         <v/>
       </c>
+      <c r="J88" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="K88" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.27586206896551724+$I$14*0.27586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="L88" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.27586206896551724+$I$15*0.27586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="M88" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.27586206896551724+$I$16*0.27586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="N88" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.27586206896551724+$I$17*0.27586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="O88" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.27586206896551724+$I$18*0.27586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="P88" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.27586206896551724+$I$19*0.27586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q88" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.27586206896551724+$I$20*0.27586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="S88" s="33" t="n">
+        <v>9</v>
+      </c>
+      <c r="T88" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.27586206896551724+$N$14*0.27586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="U88" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.27586206896551724+$N$15*0.27586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="V88" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.27586206896551724+$N$16*0.27586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="W88" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.27586206896551724+$N$17*0.27586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="X88" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.27586206896551724+$N$18*0.27586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y88" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.27586206896551724+$N$19*0.27586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z88" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.27586206896551724+$N$20*0.27586206896551724^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="16" t="n">
@@ -2143,6 +2932,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.310344827586206+$D$20*0.310344827586206^3),0)</f>
         <v/>
       </c>
+      <c r="J89" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="K89" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.3103448275862069+$I$14*0.3103448275862069^3),0)</f>
+        <v/>
+      </c>
+      <c r="L89" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.3103448275862069+$I$15*0.3103448275862069^3),0)</f>
+        <v/>
+      </c>
+      <c r="M89" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.3103448275862069+$I$16*0.3103448275862069^3),0)</f>
+        <v/>
+      </c>
+      <c r="N89" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.3103448275862069+$I$17*0.3103448275862069^3),0)</f>
+        <v/>
+      </c>
+      <c r="O89" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.3103448275862069+$I$18*0.3103448275862069^3),0)</f>
+        <v/>
+      </c>
+      <c r="P89" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.3103448275862069+$I$19*0.3103448275862069^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q89" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.3103448275862069+$I$20*0.3103448275862069^3),0)</f>
+        <v/>
+      </c>
+      <c r="S89" s="33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.3103448275862069+$N$14*0.3103448275862069^3),0)</f>
+        <v/>
+      </c>
+      <c r="U89" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.3103448275862069+$N$15*0.3103448275862069^3),0)</f>
+        <v/>
+      </c>
+      <c r="V89" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.3103448275862069+$N$16*0.3103448275862069^3),0)</f>
+        <v/>
+      </c>
+      <c r="W89" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.3103448275862069+$N$17*0.3103448275862069^3),0)</f>
+        <v/>
+      </c>
+      <c r="X89" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.3103448275862069+$N$18*0.3103448275862069^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y89" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.3103448275862069+$N$19*0.3103448275862069^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z89" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.3103448275862069+$N$20*0.3103448275862069^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="16" t="n">
@@ -2176,6 +3027,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.344827586206896+$D$20*0.344827586206896^3),0)</f>
         <v/>
       </c>
+      <c r="J90" s="33" t="n">
+        <v>11</v>
+      </c>
+      <c r="K90" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.3448275862068966+$I$14*0.3448275862068966^3),0)</f>
+        <v/>
+      </c>
+      <c r="L90" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.3448275862068966+$I$15*0.3448275862068966^3),0)</f>
+        <v/>
+      </c>
+      <c r="M90" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.3448275862068966+$I$16*0.3448275862068966^3),0)</f>
+        <v/>
+      </c>
+      <c r="N90" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.3448275862068966+$I$17*0.3448275862068966^3),0)</f>
+        <v/>
+      </c>
+      <c r="O90" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.3448275862068966+$I$18*0.3448275862068966^3),0)</f>
+        <v/>
+      </c>
+      <c r="P90" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.3448275862068966+$I$19*0.3448275862068966^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q90" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.3448275862068966+$I$20*0.3448275862068966^3),0)</f>
+        <v/>
+      </c>
+      <c r="S90" s="33" t="n">
+        <v>11</v>
+      </c>
+      <c r="T90" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.3448275862068966+$N$14*0.3448275862068966^3),0)</f>
+        <v/>
+      </c>
+      <c r="U90" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.3448275862068966+$N$15*0.3448275862068966^3),0)</f>
+        <v/>
+      </c>
+      <c r="V90" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.3448275862068966+$N$16*0.3448275862068966^3),0)</f>
+        <v/>
+      </c>
+      <c r="W90" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.3448275862068966+$N$17*0.3448275862068966^3),0)</f>
+        <v/>
+      </c>
+      <c r="X90" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.3448275862068966+$N$18*0.3448275862068966^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y90" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.3448275862068966+$N$19*0.3448275862068966^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z90" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.3448275862068966+$N$20*0.3448275862068966^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="16" t="n">
@@ -2209,6 +3122,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.379310344827586+$D$20*0.379310344827586^3),0)</f>
         <v/>
       </c>
+      <c r="J91" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="K91" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.3793103448275862+$I$14*0.3793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="L91" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.3793103448275862+$I$15*0.3793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="M91" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.3793103448275862+$I$16*0.3793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="N91" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.3793103448275862+$I$17*0.3793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="O91" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.3793103448275862+$I$18*0.3793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="P91" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.3793103448275862+$I$19*0.3793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q91" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.3793103448275862+$I$20*0.3793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="S91" s="33" t="n">
+        <v>12</v>
+      </c>
+      <c r="T91" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.3793103448275862+$N$14*0.3793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="U91" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.3793103448275862+$N$15*0.3793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="V91" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.3793103448275862+$N$16*0.3793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="W91" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.3793103448275862+$N$17*0.3793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="X91" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.3793103448275862+$N$18*0.3793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y91" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.3793103448275862+$N$19*0.3793103448275862^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z91" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.3793103448275862+$N$20*0.3793103448275862^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="16" t="n">
@@ -2242,6 +3217,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.413793103448275+$D$20*0.413793103448275^3),0)</f>
         <v/>
       </c>
+      <c r="J92" s="33" t="n">
+        <v>13</v>
+      </c>
+      <c r="K92" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.41379310344827586+$I$14*0.41379310344827586^3),0)</f>
+        <v/>
+      </c>
+      <c r="L92" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.41379310344827586+$I$15*0.41379310344827586^3),0)</f>
+        <v/>
+      </c>
+      <c r="M92" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.41379310344827586+$I$16*0.41379310344827586^3),0)</f>
+        <v/>
+      </c>
+      <c r="N92" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.41379310344827586+$I$17*0.41379310344827586^3),0)</f>
+        <v/>
+      </c>
+      <c r="O92" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.41379310344827586+$I$18*0.41379310344827586^3),0)</f>
+        <v/>
+      </c>
+      <c r="P92" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.41379310344827586+$I$19*0.41379310344827586^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q92" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.41379310344827586+$I$20*0.41379310344827586^3),0)</f>
+        <v/>
+      </c>
+      <c r="S92" s="33" t="n">
+        <v>13</v>
+      </c>
+      <c r="T92" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.41379310344827586+$N$14*0.41379310344827586^3),0)</f>
+        <v/>
+      </c>
+      <c r="U92" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.41379310344827586+$N$15*0.41379310344827586^3),0)</f>
+        <v/>
+      </c>
+      <c r="V92" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.41379310344827586+$N$16*0.41379310344827586^3),0)</f>
+        <v/>
+      </c>
+      <c r="W92" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.41379310344827586+$N$17*0.41379310344827586^3),0)</f>
+        <v/>
+      </c>
+      <c r="X92" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.41379310344827586+$N$18*0.41379310344827586^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y92" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.41379310344827586+$N$19*0.41379310344827586^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z92" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.41379310344827586+$N$20*0.41379310344827586^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="93">
       <c r="A93" s="16" t="n">
@@ -2275,6 +3312,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.448275862068965+$D$20*0.448275862068965^3),0)</f>
         <v/>
       </c>
+      <c r="J93" s="33" t="n">
+        <v>14</v>
+      </c>
+      <c r="K93" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.4482758620689655+$I$14*0.4482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="L93" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.4482758620689655+$I$15*0.4482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="M93" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.4482758620689655+$I$16*0.4482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="N93" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.4482758620689655+$I$17*0.4482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="O93" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.4482758620689655+$I$18*0.4482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="P93" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.4482758620689655+$I$19*0.4482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q93" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.4482758620689655+$I$20*0.4482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="S93" s="33" t="n">
+        <v>14</v>
+      </c>
+      <c r="T93" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.4482758620689655+$N$14*0.4482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="U93" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.4482758620689655+$N$15*0.4482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="V93" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.4482758620689655+$N$16*0.4482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="W93" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.4482758620689655+$N$17*0.4482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="X93" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.4482758620689655+$N$18*0.4482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y93" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.4482758620689655+$N$19*0.4482758620689655^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z93" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.4482758620689655+$N$20*0.4482758620689655^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="16" t="n">
@@ -2308,6 +3407,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.482758620689655+$D$20*0.482758620689655^3),0)</f>
         <v/>
       </c>
+      <c r="J94" s="33" t="n">
+        <v>15</v>
+      </c>
+      <c r="K94" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.4827586206896552+$I$14*0.4827586206896552^3),0)</f>
+        <v/>
+      </c>
+      <c r="L94" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.4827586206896552+$I$15*0.4827586206896552^3),0)</f>
+        <v/>
+      </c>
+      <c r="M94" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.4827586206896552+$I$16*0.4827586206896552^3),0)</f>
+        <v/>
+      </c>
+      <c r="N94" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.4827586206896552+$I$17*0.4827586206896552^3),0)</f>
+        <v/>
+      </c>
+      <c r="O94" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.4827586206896552+$I$18*0.4827586206896552^3),0)</f>
+        <v/>
+      </c>
+      <c r="P94" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.4827586206896552+$I$19*0.4827586206896552^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q94" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.4827586206896552+$I$20*0.4827586206896552^3),0)</f>
+        <v/>
+      </c>
+      <c r="S94" s="33" t="n">
+        <v>15</v>
+      </c>
+      <c r="T94" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.4827586206896552+$N$14*0.4827586206896552^3),0)</f>
+        <v/>
+      </c>
+      <c r="U94" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.4827586206896552+$N$15*0.4827586206896552^3),0)</f>
+        <v/>
+      </c>
+      <c r="V94" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.4827586206896552+$N$16*0.4827586206896552^3),0)</f>
+        <v/>
+      </c>
+      <c r="W94" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.4827586206896552+$N$17*0.4827586206896552^3),0)</f>
+        <v/>
+      </c>
+      <c r="X94" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.4827586206896552+$N$18*0.4827586206896552^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y94" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.4827586206896552+$N$19*0.4827586206896552^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z94" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.4827586206896552+$N$20*0.4827586206896552^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="16" t="n">
@@ -2341,6 +3502,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.517241379310344+$D$20*0.517241379310344^3),0)</f>
         <v/>
       </c>
+      <c r="J95" s="33" t="n">
+        <v>16</v>
+      </c>
+      <c r="K95" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.5172413793103449+$I$14*0.5172413793103449^3),0)</f>
+        <v/>
+      </c>
+      <c r="L95" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.5172413793103449+$I$15*0.5172413793103449^3),0)</f>
+        <v/>
+      </c>
+      <c r="M95" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.5172413793103449+$I$16*0.5172413793103449^3),0)</f>
+        <v/>
+      </c>
+      <c r="N95" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.5172413793103449+$I$17*0.5172413793103449^3),0)</f>
+        <v/>
+      </c>
+      <c r="O95" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.5172413793103449+$I$18*0.5172413793103449^3),0)</f>
+        <v/>
+      </c>
+      <c r="P95" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.5172413793103449+$I$19*0.5172413793103449^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q95" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.5172413793103449+$I$20*0.5172413793103449^3),0)</f>
+        <v/>
+      </c>
+      <c r="S95" s="33" t="n">
+        <v>16</v>
+      </c>
+      <c r="T95" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.5172413793103449+$N$14*0.5172413793103449^3),0)</f>
+        <v/>
+      </c>
+      <c r="U95" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.5172413793103449+$N$15*0.5172413793103449^3),0)</f>
+        <v/>
+      </c>
+      <c r="V95" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.5172413793103449+$N$16*0.5172413793103449^3),0)</f>
+        <v/>
+      </c>
+      <c r="W95" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.5172413793103449+$N$17*0.5172413793103449^3),0)</f>
+        <v/>
+      </c>
+      <c r="X95" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.5172413793103449+$N$18*0.5172413793103449^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y95" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.5172413793103449+$N$19*0.5172413793103449^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z95" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.5172413793103449+$N$20*0.5172413793103449^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="16" t="n">
@@ -2374,6 +3597,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.551724137931034+$D$20*0.551724137931034^3),0)</f>
         <v/>
       </c>
+      <c r="J96" s="33" t="n">
+        <v>17</v>
+      </c>
+      <c r="K96" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.5517241379310345+$I$14*0.5517241379310345^3),0)</f>
+        <v/>
+      </c>
+      <c r="L96" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.5517241379310345+$I$15*0.5517241379310345^3),0)</f>
+        <v/>
+      </c>
+      <c r="M96" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.5517241379310345+$I$16*0.5517241379310345^3),0)</f>
+        <v/>
+      </c>
+      <c r="N96" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.5517241379310345+$I$17*0.5517241379310345^3),0)</f>
+        <v/>
+      </c>
+      <c r="O96" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.5517241379310345+$I$18*0.5517241379310345^3),0)</f>
+        <v/>
+      </c>
+      <c r="P96" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.5517241379310345+$I$19*0.5517241379310345^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q96" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.5517241379310345+$I$20*0.5517241379310345^3),0)</f>
+        <v/>
+      </c>
+      <c r="S96" s="33" t="n">
+        <v>17</v>
+      </c>
+      <c r="T96" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.5517241379310345+$N$14*0.5517241379310345^3),0)</f>
+        <v/>
+      </c>
+      <c r="U96" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.5517241379310345+$N$15*0.5517241379310345^3),0)</f>
+        <v/>
+      </c>
+      <c r="V96" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.5517241379310345+$N$16*0.5517241379310345^3),0)</f>
+        <v/>
+      </c>
+      <c r="W96" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.5517241379310345+$N$17*0.5517241379310345^3),0)</f>
+        <v/>
+      </c>
+      <c r="X96" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.5517241379310345+$N$18*0.5517241379310345^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y96" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.5517241379310345+$N$19*0.5517241379310345^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z96" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.5517241379310345+$N$20*0.5517241379310345^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="16" t="n">
@@ -2407,6 +3692,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.586206896551724+$D$20*0.586206896551724^3),0)</f>
         <v/>
       </c>
+      <c r="J97" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="K97" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.5862068965517241+$I$14*0.5862068965517241^3),0)</f>
+        <v/>
+      </c>
+      <c r="L97" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.5862068965517241+$I$15*0.5862068965517241^3),0)</f>
+        <v/>
+      </c>
+      <c r="M97" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.5862068965517241+$I$16*0.5862068965517241^3),0)</f>
+        <v/>
+      </c>
+      <c r="N97" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.5862068965517241+$I$17*0.5862068965517241^3),0)</f>
+        <v/>
+      </c>
+      <c r="O97" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.5862068965517241+$I$18*0.5862068965517241^3),0)</f>
+        <v/>
+      </c>
+      <c r="P97" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.5862068965517241+$I$19*0.5862068965517241^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q97" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.5862068965517241+$I$20*0.5862068965517241^3),0)</f>
+        <v/>
+      </c>
+      <c r="S97" s="33" t="n">
+        <v>18</v>
+      </c>
+      <c r="T97" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.5862068965517241+$N$14*0.5862068965517241^3),0)</f>
+        <v/>
+      </c>
+      <c r="U97" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.5862068965517241+$N$15*0.5862068965517241^3),0)</f>
+        <v/>
+      </c>
+      <c r="V97" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.5862068965517241+$N$16*0.5862068965517241^3),0)</f>
+        <v/>
+      </c>
+      <c r="W97" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.5862068965517241+$N$17*0.5862068965517241^3),0)</f>
+        <v/>
+      </c>
+      <c r="X97" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.5862068965517241+$N$18*0.5862068965517241^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y97" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.5862068965517241+$N$19*0.5862068965517241^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z97" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.5862068965517241+$N$20*0.5862068965517241^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="16" t="n">
@@ -2440,6 +3787,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.620689655172413+$D$20*0.620689655172413^3),0)</f>
         <v/>
       </c>
+      <c r="J98" s="33" t="n">
+        <v>19</v>
+      </c>
+      <c r="K98" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.6206896551724138+$I$14*0.6206896551724138^3),0)</f>
+        <v/>
+      </c>
+      <c r="L98" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.6206896551724138+$I$15*0.6206896551724138^3),0)</f>
+        <v/>
+      </c>
+      <c r="M98" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.6206896551724138+$I$16*0.6206896551724138^3),0)</f>
+        <v/>
+      </c>
+      <c r="N98" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.6206896551724138+$I$17*0.6206896551724138^3),0)</f>
+        <v/>
+      </c>
+      <c r="O98" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.6206896551724138+$I$18*0.6206896551724138^3),0)</f>
+        <v/>
+      </c>
+      <c r="P98" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.6206896551724138+$I$19*0.6206896551724138^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q98" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.6206896551724138+$I$20*0.6206896551724138^3),0)</f>
+        <v/>
+      </c>
+      <c r="S98" s="33" t="n">
+        <v>19</v>
+      </c>
+      <c r="T98" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.6206896551724138+$N$14*0.6206896551724138^3),0)</f>
+        <v/>
+      </c>
+      <c r="U98" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.6206896551724138+$N$15*0.6206896551724138^3),0)</f>
+        <v/>
+      </c>
+      <c r="V98" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.6206896551724138+$N$16*0.6206896551724138^3),0)</f>
+        <v/>
+      </c>
+      <c r="W98" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.6206896551724138+$N$17*0.6206896551724138^3),0)</f>
+        <v/>
+      </c>
+      <c r="X98" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.6206896551724138+$N$18*0.6206896551724138^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y98" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.6206896551724138+$N$19*0.6206896551724138^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z98" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.6206896551724138+$N$20*0.6206896551724138^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="16" t="n">
@@ -2473,6 +3882,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.655172413793103+$D$20*0.655172413793103^3),0)</f>
         <v/>
       </c>
+      <c r="J99" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="K99" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.6551724137931034+$I$14*0.6551724137931034^3),0)</f>
+        <v/>
+      </c>
+      <c r="L99" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.6551724137931034+$I$15*0.6551724137931034^3),0)</f>
+        <v/>
+      </c>
+      <c r="M99" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.6551724137931034+$I$16*0.6551724137931034^3),0)</f>
+        <v/>
+      </c>
+      <c r="N99" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.6551724137931034+$I$17*0.6551724137931034^3),0)</f>
+        <v/>
+      </c>
+      <c r="O99" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.6551724137931034+$I$18*0.6551724137931034^3),0)</f>
+        <v/>
+      </c>
+      <c r="P99" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.6551724137931034+$I$19*0.6551724137931034^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q99" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.6551724137931034+$I$20*0.6551724137931034^3),0)</f>
+        <v/>
+      </c>
+      <c r="S99" s="33" t="n">
+        <v>20</v>
+      </c>
+      <c r="T99" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.6551724137931034+$N$14*0.6551724137931034^3),0)</f>
+        <v/>
+      </c>
+      <c r="U99" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.6551724137931034+$N$15*0.6551724137931034^3),0)</f>
+        <v/>
+      </c>
+      <c r="V99" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.6551724137931034+$N$16*0.6551724137931034^3),0)</f>
+        <v/>
+      </c>
+      <c r="W99" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.6551724137931034+$N$17*0.6551724137931034^3),0)</f>
+        <v/>
+      </c>
+      <c r="X99" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.6551724137931034+$N$18*0.6551724137931034^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y99" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.6551724137931034+$N$19*0.6551724137931034^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z99" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.6551724137931034+$N$20*0.6551724137931034^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="16" t="n">
@@ -2506,6 +3977,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.689655172413793+$D$20*0.689655172413793^3),0)</f>
         <v/>
       </c>
+      <c r="J100" s="33" t="n">
+        <v>21</v>
+      </c>
+      <c r="K100" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.6896551724137931+$I$14*0.6896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="L100" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.6896551724137931+$I$15*0.6896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="M100" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.6896551724137931+$I$16*0.6896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="N100" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.6896551724137931+$I$17*0.6896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="O100" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.6896551724137931+$I$18*0.6896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="P100" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.6896551724137931+$I$19*0.6896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q100" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.6896551724137931+$I$20*0.6896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="S100" s="33" t="n">
+        <v>21</v>
+      </c>
+      <c r="T100" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.6896551724137931+$N$14*0.6896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="U100" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.6896551724137931+$N$15*0.6896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="V100" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.6896551724137931+$N$16*0.6896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="W100" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.6896551724137931+$N$17*0.6896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="X100" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.6896551724137931+$N$18*0.6896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y100" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.6896551724137931+$N$19*0.6896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z100" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.6896551724137931+$N$20*0.6896551724137931^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="16" t="n">
@@ -2539,6 +4072,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.724137931034482+$D$20*0.724137931034482^3),0)</f>
         <v/>
       </c>
+      <c r="J101" s="33" t="n">
+        <v>22</v>
+      </c>
+      <c r="K101" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.7241379310344828+$I$14*0.7241379310344828^3),0)</f>
+        <v/>
+      </c>
+      <c r="L101" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.7241379310344828+$I$15*0.7241379310344828^3),0)</f>
+        <v/>
+      </c>
+      <c r="M101" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.7241379310344828+$I$16*0.7241379310344828^3),0)</f>
+        <v/>
+      </c>
+      <c r="N101" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.7241379310344828+$I$17*0.7241379310344828^3),0)</f>
+        <v/>
+      </c>
+      <c r="O101" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.7241379310344828+$I$18*0.7241379310344828^3),0)</f>
+        <v/>
+      </c>
+      <c r="P101" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.7241379310344828+$I$19*0.7241379310344828^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q101" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.7241379310344828+$I$20*0.7241379310344828^3),0)</f>
+        <v/>
+      </c>
+      <c r="S101" s="33" t="n">
+        <v>22</v>
+      </c>
+      <c r="T101" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.7241379310344828+$N$14*0.7241379310344828^3),0)</f>
+        <v/>
+      </c>
+      <c r="U101" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.7241379310344828+$N$15*0.7241379310344828^3),0)</f>
+        <v/>
+      </c>
+      <c r="V101" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.7241379310344828+$N$16*0.7241379310344828^3),0)</f>
+        <v/>
+      </c>
+      <c r="W101" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.7241379310344828+$N$17*0.7241379310344828^3),0)</f>
+        <v/>
+      </c>
+      <c r="X101" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.7241379310344828+$N$18*0.7241379310344828^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y101" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.7241379310344828+$N$19*0.7241379310344828^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z101" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.7241379310344828+$N$20*0.7241379310344828^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="16" t="n">
@@ -2572,6 +4167,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.758620689655172+$D$20*0.758620689655172^3),0)</f>
         <v/>
       </c>
+      <c r="J102" s="33" t="n">
+        <v>23</v>
+      </c>
+      <c r="K102" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.7586206896551724+$I$14*0.7586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="L102" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.7586206896551724+$I$15*0.7586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="M102" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.7586206896551724+$I$16*0.7586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="N102" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.7586206896551724+$I$17*0.7586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="O102" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.7586206896551724+$I$18*0.7586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="P102" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.7586206896551724+$I$19*0.7586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q102" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.7586206896551724+$I$20*0.7586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="S102" s="33" t="n">
+        <v>23</v>
+      </c>
+      <c r="T102" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.7586206896551724+$N$14*0.7586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="U102" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.7586206896551724+$N$15*0.7586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="V102" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.7586206896551724+$N$16*0.7586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="W102" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.7586206896551724+$N$17*0.7586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="X102" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.7586206896551724+$N$18*0.7586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y102" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.7586206896551724+$N$19*0.7586206896551724^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z102" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.7586206896551724+$N$20*0.7586206896551724^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="16" t="n">
@@ -2605,6 +4262,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.793103448275862+$D$20*0.793103448275862^3),0)</f>
         <v/>
       </c>
+      <c r="J103" s="33" t="n">
+        <v>24</v>
+      </c>
+      <c r="K103" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.7931034482758621+$I$14*0.7931034482758621^3),0)</f>
+        <v/>
+      </c>
+      <c r="L103" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.7931034482758621+$I$15*0.7931034482758621^3),0)</f>
+        <v/>
+      </c>
+      <c r="M103" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.7931034482758621+$I$16*0.7931034482758621^3),0)</f>
+        <v/>
+      </c>
+      <c r="N103" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.7931034482758621+$I$17*0.7931034482758621^3),0)</f>
+        <v/>
+      </c>
+      <c r="O103" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.7931034482758621+$I$18*0.7931034482758621^3),0)</f>
+        <v/>
+      </c>
+      <c r="P103" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.7931034482758621+$I$19*0.7931034482758621^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q103" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.7931034482758621+$I$20*0.7931034482758621^3),0)</f>
+        <v/>
+      </c>
+      <c r="S103" s="33" t="n">
+        <v>24</v>
+      </c>
+      <c r="T103" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.7931034482758621+$N$14*0.7931034482758621^3),0)</f>
+        <v/>
+      </c>
+      <c r="U103" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.7931034482758621+$N$15*0.7931034482758621^3),0)</f>
+        <v/>
+      </c>
+      <c r="V103" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.7931034482758621+$N$16*0.7931034482758621^3),0)</f>
+        <v/>
+      </c>
+      <c r="W103" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.7931034482758621+$N$17*0.7931034482758621^3),0)</f>
+        <v/>
+      </c>
+      <c r="X103" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.7931034482758621+$N$18*0.7931034482758621^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y103" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.7931034482758621+$N$19*0.7931034482758621^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z103" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.7931034482758621+$N$20*0.7931034482758621^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="16" t="n">
@@ -2638,6 +4357,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.827586206896551+$D$20*0.827586206896551^3),0)</f>
         <v/>
       </c>
+      <c r="J104" s="33" t="n">
+        <v>25</v>
+      </c>
+      <c r="K104" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.8275862068965517+$I$14*0.8275862068965517^3),0)</f>
+        <v/>
+      </c>
+      <c r="L104" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.8275862068965517+$I$15*0.8275862068965517^3),0)</f>
+        <v/>
+      </c>
+      <c r="M104" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.8275862068965517+$I$16*0.8275862068965517^3),0)</f>
+        <v/>
+      </c>
+      <c r="N104" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.8275862068965517+$I$17*0.8275862068965517^3),0)</f>
+        <v/>
+      </c>
+      <c r="O104" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.8275862068965517+$I$18*0.8275862068965517^3),0)</f>
+        <v/>
+      </c>
+      <c r="P104" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.8275862068965517+$I$19*0.8275862068965517^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q104" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.8275862068965517+$I$20*0.8275862068965517^3),0)</f>
+        <v/>
+      </c>
+      <c r="S104" s="33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T104" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.8275862068965517+$N$14*0.8275862068965517^3),0)</f>
+        <v/>
+      </c>
+      <c r="U104" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.8275862068965517+$N$15*0.8275862068965517^3),0)</f>
+        <v/>
+      </c>
+      <c r="V104" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.8275862068965517+$N$16*0.8275862068965517^3),0)</f>
+        <v/>
+      </c>
+      <c r="W104" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.8275862068965517+$N$17*0.8275862068965517^3),0)</f>
+        <v/>
+      </c>
+      <c r="X104" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.8275862068965517+$N$18*0.8275862068965517^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y104" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.8275862068965517+$N$19*0.8275862068965517^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z104" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.8275862068965517+$N$20*0.8275862068965517^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="16" t="n">
@@ -2671,6 +4452,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.862068965517241+$D$20*0.862068965517241^3),0)</f>
         <v/>
       </c>
+      <c r="J105" s="33" t="n">
+        <v>26</v>
+      </c>
+      <c r="K105" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.8620689655172413+$I$14*0.8620689655172413^3),0)</f>
+        <v/>
+      </c>
+      <c r="L105" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.8620689655172413+$I$15*0.8620689655172413^3),0)</f>
+        <v/>
+      </c>
+      <c r="M105" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.8620689655172413+$I$16*0.8620689655172413^3),0)</f>
+        <v/>
+      </c>
+      <c r="N105" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.8620689655172413+$I$17*0.8620689655172413^3),0)</f>
+        <v/>
+      </c>
+      <c r="O105" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.8620689655172413+$I$18*0.8620689655172413^3),0)</f>
+        <v/>
+      </c>
+      <c r="P105" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.8620689655172413+$I$19*0.8620689655172413^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q105" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.8620689655172413+$I$20*0.8620689655172413^3),0)</f>
+        <v/>
+      </c>
+      <c r="S105" s="33" t="n">
+        <v>26</v>
+      </c>
+      <c r="T105" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.8620689655172413+$N$14*0.8620689655172413^3),0)</f>
+        <v/>
+      </c>
+      <c r="U105" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.8620689655172413+$N$15*0.8620689655172413^3),0)</f>
+        <v/>
+      </c>
+      <c r="V105" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.8620689655172413+$N$16*0.8620689655172413^3),0)</f>
+        <v/>
+      </c>
+      <c r="W105" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.8620689655172413+$N$17*0.8620689655172413^3),0)</f>
+        <v/>
+      </c>
+      <c r="X105" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.8620689655172413+$N$18*0.8620689655172413^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y105" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.8620689655172413+$N$19*0.8620689655172413^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z105" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.8620689655172413+$N$20*0.8620689655172413^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="16" t="n">
@@ -2704,6 +4547,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.896551724137931+$D$20*0.896551724137931^3),0)</f>
         <v/>
       </c>
+      <c r="J106" s="33" t="n">
+        <v>27</v>
+      </c>
+      <c r="K106" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.896551724137931+$I$14*0.896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="L106" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.896551724137931+$I$15*0.896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="M106" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.896551724137931+$I$16*0.896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="N106" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.896551724137931+$I$17*0.896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="O106" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.896551724137931+$I$18*0.896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="P106" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.896551724137931+$I$19*0.896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q106" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.896551724137931+$I$20*0.896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="S106" s="33" t="n">
+        <v>27</v>
+      </c>
+      <c r="T106" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.896551724137931+$N$14*0.896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="U106" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.896551724137931+$N$15*0.896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="V106" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.896551724137931+$N$16*0.896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="W106" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.896551724137931+$N$17*0.896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="X106" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.896551724137931+$N$18*0.896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y106" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.896551724137931+$N$19*0.896551724137931^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z106" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.896551724137931+$N$20*0.896551724137931^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="16" t="n">
@@ -2737,6 +4642,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.93103448275862+$D$20*0.93103448275862^3),0)</f>
         <v/>
       </c>
+      <c r="J107" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="K107" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.9310344827586207+$I$14*0.9310344827586207^3),0)</f>
+        <v/>
+      </c>
+      <c r="L107" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.9310344827586207+$I$15*0.9310344827586207^3),0)</f>
+        <v/>
+      </c>
+      <c r="M107" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.9310344827586207+$I$16*0.9310344827586207^3),0)</f>
+        <v/>
+      </c>
+      <c r="N107" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.9310344827586207+$I$17*0.9310344827586207^3),0)</f>
+        <v/>
+      </c>
+      <c r="O107" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.9310344827586207+$I$18*0.9310344827586207^3),0)</f>
+        <v/>
+      </c>
+      <c r="P107" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.9310344827586207+$I$19*0.9310344827586207^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q107" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.9310344827586207+$I$20*0.9310344827586207^3),0)</f>
+        <v/>
+      </c>
+      <c r="S107" s="33" t="n">
+        <v>28</v>
+      </c>
+      <c r="T107" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.9310344827586207+$N$14*0.9310344827586207^3),0)</f>
+        <v/>
+      </c>
+      <c r="U107" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.9310344827586207+$N$15*0.9310344827586207^3),0)</f>
+        <v/>
+      </c>
+      <c r="V107" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.9310344827586207+$N$16*0.9310344827586207^3),0)</f>
+        <v/>
+      </c>
+      <c r="W107" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.9310344827586207+$N$17*0.9310344827586207^3),0)</f>
+        <v/>
+      </c>
+      <c r="X107" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.9310344827586207+$N$18*0.9310344827586207^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y107" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.9310344827586207+$N$19*0.9310344827586207^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z107" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.9310344827586207+$N$20*0.9310344827586207^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="16" t="n">
@@ -2770,6 +4737,68 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*0.96551724137931+$D$20*0.96551724137931^3),0)</f>
         <v/>
       </c>
+      <c r="J108" s="33" t="n">
+        <v>29</v>
+      </c>
+      <c r="K108" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*0.9655172413793104+$I$14*0.9655172413793104^3),0)</f>
+        <v/>
+      </c>
+      <c r="L108" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*0.9655172413793104+$I$15*0.9655172413793104^3),0)</f>
+        <v/>
+      </c>
+      <c r="M108" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*0.9655172413793104+$I$16*0.9655172413793104^3),0)</f>
+        <v/>
+      </c>
+      <c r="N108" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*0.9655172413793104+$I$17*0.9655172413793104^3),0)</f>
+        <v/>
+      </c>
+      <c r="O108" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*0.9655172413793104+$I$18*0.9655172413793104^3),0)</f>
+        <v/>
+      </c>
+      <c r="P108" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*0.9655172413793104+$I$19*0.9655172413793104^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q108" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*0.9655172413793104+$I$20*0.9655172413793104^3),0)</f>
+        <v/>
+      </c>
+      <c r="S108" s="33" t="n">
+        <v>29</v>
+      </c>
+      <c r="T108" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*0.9655172413793104+$N$14*0.9655172413793104^3),0)</f>
+        <v/>
+      </c>
+      <c r="U108" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*0.9655172413793104+$N$15*0.9655172413793104^3),0)</f>
+        <v/>
+      </c>
+      <c r="V108" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*0.9655172413793104+$N$16*0.9655172413793104^3),0)</f>
+        <v/>
+      </c>
+      <c r="W108" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*0.9655172413793104+$N$17*0.9655172413793104^3),0)</f>
+        <v/>
+      </c>
+      <c r="X108" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*0.9655172413793104+$N$18*0.9655172413793104^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y108" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*0.9655172413793104+$N$19*0.9655172413793104^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z108" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*0.9655172413793104+$N$20*0.9655172413793104^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="16" t="n">
@@ -2803,2084 +4832,718 @@
         <f>ROUND($B$20+($C$20-$B$20)*((1-$D$20)*1+$D$20*1^3),0)</f>
         <v/>
       </c>
+      <c r="J109" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="K109" s="33">
+        <f>ROUND($G$14+($H$14-$G$14)*((1-$I$14)*1.0+$I$14*1.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="L109" s="33">
+        <f>ROUND($G$15+($H$15-$G$15)*((1-$I$15)*1.0+$I$15*1.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="M109" s="33">
+        <f>ROUND($G$16+($H$16-$G$16)*((1-$I$16)*1.0+$I$16*1.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="N109" s="33">
+        <f>ROUND($G$17+($H$17-$G$17)*((1-$I$17)*1.0+$I$17*1.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="O109" s="33">
+        <f>ROUND($G$18+($H$18-$G$18)*((1-$I$18)*1.0+$I$18*1.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="P109" s="33">
+        <f>ROUND($G$19+($H$19-$G$19)*((1-$I$19)*1.0+$I$19*1.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="Q109" s="33">
+        <f>ROUND($G$20+($H$20-$G$20)*((1-$I$20)*1.0+$I$20*1.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="S109" s="33" t="n">
+        <v>30</v>
+      </c>
+      <c r="T109" s="33">
+        <f>ROUND($L$14+($M$14-$L$14)*((1-$N$14)*1.0+$N$14*1.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="U109" s="33">
+        <f>ROUND($L$15+($M$15-$L$15)*((1-$N$15)*1.0+$N$15*1.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="V109" s="33">
+        <f>ROUND($L$16+($M$16-$L$16)*((1-$N$16)*1.0+$N$16*1.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="W109" s="33">
+        <f>ROUND($L$17+($M$17-$L$17)*((1-$N$17)*1.0+$N$17*1.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="X109" s="33">
+        <f>ROUND($L$18+($M$18-$L$18)*((1-$N$18)*1.0+$N$18*1.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="Y109" s="33">
+        <f>ROUND($L$19+($M$19-$L$19)*((1-$N$19)*1.0+$N$19*1.0^3),0)</f>
+        <v/>
+      </c>
+      <c r="Z109" s="33">
+        <f>ROUND($L$20+($M$20-$L$20)*((1-$N$20)*1.0+$N$20*1.0^3),0)</f>
+        <v/>
+      </c>
     </row>
     <row r="111">
-      <c r="A111" s="28" t="inlineStr">
-        <is>
-          <t>[물리딜러 (가칭)] 레벨 1~30 스탯 (자동 계산)</t>
-        </is>
-      </c>
+      <c r="A111" s="34" t="n"/>
+      <c r="B111" s="34" t="n"/>
+      <c r="C111" s="34" t="n"/>
+      <c r="D111" s="34" t="n"/>
+      <c r="E111" s="34" t="n"/>
+      <c r="F111" s="34" t="n"/>
+      <c r="G111" s="34" t="n"/>
+      <c r="H111" s="34" t="n"/>
     </row>
     <row r="112" ht="18" customHeight="1" s="24">
-      <c r="A112" s="14" t="inlineStr">
-        <is>
-          <t>레벨</t>
-        </is>
-      </c>
-      <c r="B112" s="14" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="C112" s="14" t="inlineStr">
-        <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="D112" s="14" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="E112" s="14" t="inlineStr">
-        <is>
-          <t>속도</t>
-        </is>
-      </c>
-      <c r="F112" s="14" t="inlineStr">
-        <is>
-          <t>힘</t>
-        </is>
-      </c>
-      <c r="G112" s="14" t="inlineStr">
-        <is>
-          <t>지력</t>
-        </is>
-      </c>
-      <c r="H112" s="14" t="inlineStr">
-        <is>
-          <t>치료효율</t>
-        </is>
-      </c>
+      <c r="A112" s="34" t="n"/>
+      <c r="B112" s="34" t="n"/>
+      <c r="C112" s="34" t="n"/>
+      <c r="D112" s="34" t="n"/>
+      <c r="E112" s="34" t="n"/>
+      <c r="F112" s="34" t="n"/>
+      <c r="G112" s="34" t="n"/>
+      <c r="H112" s="34" t="n"/>
     </row>
     <row r="113">
-      <c r="A113" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B113" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0+$D$25*0^3),0)</f>
-        <v/>
-      </c>
-      <c r="C113" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0+$D$26*0^3),0)</f>
-        <v/>
-      </c>
-      <c r="D113" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0+$D$27*0^3),0)</f>
-        <v/>
-      </c>
-      <c r="E113" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0+$D$28*0^3),0)</f>
-        <v/>
-      </c>
-      <c r="F113" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0+$D$29*0^3),0)</f>
-        <v/>
-      </c>
-      <c r="G113" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0+$D$30*0^3),0)</f>
-        <v/>
-      </c>
-      <c r="H113" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0+$D$31*0^3),0)</f>
-        <v/>
-      </c>
+      <c r="A113" s="34" t="n"/>
+      <c r="B113" s="34" t="n"/>
+      <c r="C113" s="34" t="n"/>
+      <c r="D113" s="34" t="n"/>
+      <c r="E113" s="34" t="n"/>
+      <c r="F113" s="34" t="n"/>
+      <c r="G113" s="34" t="n"/>
+      <c r="H113" s="34" t="n"/>
     </row>
     <row r="114">
-      <c r="A114" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B114" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.0344827586206896+$D$25*0.0344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="C114" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.0344827586206896+$D$26*0.0344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="D114" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.0344827586206896+$D$27*0.0344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="E114" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.0344827586206896+$D$28*0.0344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="F114" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.0344827586206896+$D$29*0.0344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="G114" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.0344827586206896+$D$30*0.0344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="H114" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.0344827586206896+$D$31*0.0344827586206896^3),0)</f>
-        <v/>
-      </c>
+      <c r="A114" s="34" t="n"/>
+      <c r="B114" s="34" t="n"/>
+      <c r="C114" s="34" t="n"/>
+      <c r="D114" s="34" t="n"/>
+      <c r="E114" s="34" t="n"/>
+      <c r="F114" s="34" t="n"/>
+      <c r="G114" s="34" t="n"/>
+      <c r="H114" s="34" t="n"/>
     </row>
     <row r="115">
-      <c r="A115" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B115" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.0689655172413793+$D$25*0.0689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="C115" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.0689655172413793+$D$26*0.0689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="D115" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.0689655172413793+$D$27*0.0689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="E115" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.0689655172413793+$D$28*0.0689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="F115" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.0689655172413793+$D$29*0.0689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="G115" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.0689655172413793+$D$30*0.0689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="H115" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.0689655172413793+$D$31*0.0689655172413793^3),0)</f>
-        <v/>
-      </c>
+      <c r="A115" s="34" t="n"/>
+      <c r="B115" s="34" t="n"/>
+      <c r="C115" s="34" t="n"/>
+      <c r="D115" s="34" t="n"/>
+      <c r="E115" s="34" t="n"/>
+      <c r="F115" s="34" t="n"/>
+      <c r="G115" s="34" t="n"/>
+      <c r="H115" s="34" t="n"/>
     </row>
     <row r="116">
-      <c r="A116" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B116" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.103448275862068+$D$25*0.103448275862068^3),0)</f>
-        <v/>
-      </c>
-      <c r="C116" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.103448275862068+$D$26*0.103448275862068^3),0)</f>
-        <v/>
-      </c>
-      <c r="D116" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.103448275862068+$D$27*0.103448275862068^3),0)</f>
-        <v/>
-      </c>
-      <c r="E116" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.103448275862068+$D$28*0.103448275862068^3),0)</f>
-        <v/>
-      </c>
-      <c r="F116" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.103448275862068+$D$29*0.103448275862068^3),0)</f>
-        <v/>
-      </c>
-      <c r="G116" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.103448275862068+$D$30*0.103448275862068^3),0)</f>
-        <v/>
-      </c>
-      <c r="H116" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.103448275862068+$D$31*0.103448275862068^3),0)</f>
-        <v/>
-      </c>
+      <c r="A116" s="34" t="n"/>
+      <c r="B116" s="34" t="n"/>
+      <c r="C116" s="34" t="n"/>
+      <c r="D116" s="34" t="n"/>
+      <c r="E116" s="34" t="n"/>
+      <c r="F116" s="34" t="n"/>
+      <c r="G116" s="34" t="n"/>
+      <c r="H116" s="34" t="n"/>
     </row>
     <row r="117">
-      <c r="A117" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B117" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.137931034482758+$D$25*0.137931034482758^3),0)</f>
-        <v/>
-      </c>
-      <c r="C117" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.137931034482758+$D$26*0.137931034482758^3),0)</f>
-        <v/>
-      </c>
-      <c r="D117" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.137931034482758+$D$27*0.137931034482758^3),0)</f>
-        <v/>
-      </c>
-      <c r="E117" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.137931034482758+$D$28*0.137931034482758^3),0)</f>
-        <v/>
-      </c>
-      <c r="F117" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.137931034482758+$D$29*0.137931034482758^3),0)</f>
-        <v/>
-      </c>
-      <c r="G117" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.137931034482758+$D$30*0.137931034482758^3),0)</f>
-        <v/>
-      </c>
-      <c r="H117" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.137931034482758+$D$31*0.137931034482758^3),0)</f>
-        <v/>
-      </c>
+      <c r="A117" s="34" t="n"/>
+      <c r="B117" s="34" t="n"/>
+      <c r="C117" s="34" t="n"/>
+      <c r="D117" s="34" t="n"/>
+      <c r="E117" s="34" t="n"/>
+      <c r="F117" s="34" t="n"/>
+      <c r="G117" s="34" t="n"/>
+      <c r="H117" s="34" t="n"/>
     </row>
     <row r="118">
-      <c r="A118" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="B118" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.172413793103448+$D$25*0.172413793103448^3),0)</f>
-        <v/>
-      </c>
-      <c r="C118" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.172413793103448+$D$26*0.172413793103448^3),0)</f>
-        <v/>
-      </c>
-      <c r="D118" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.172413793103448+$D$27*0.172413793103448^3),0)</f>
-        <v/>
-      </c>
-      <c r="E118" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.172413793103448+$D$28*0.172413793103448^3),0)</f>
-        <v/>
-      </c>
-      <c r="F118" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.172413793103448+$D$29*0.172413793103448^3),0)</f>
-        <v/>
-      </c>
-      <c r="G118" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.172413793103448+$D$30*0.172413793103448^3),0)</f>
-        <v/>
-      </c>
-      <c r="H118" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.172413793103448+$D$31*0.172413793103448^3),0)</f>
-        <v/>
-      </c>
+      <c r="A118" s="34" t="n"/>
+      <c r="B118" s="34" t="n"/>
+      <c r="C118" s="34" t="n"/>
+      <c r="D118" s="34" t="n"/>
+      <c r="E118" s="34" t="n"/>
+      <c r="F118" s="34" t="n"/>
+      <c r="G118" s="34" t="n"/>
+      <c r="H118" s="34" t="n"/>
     </row>
     <row r="119">
-      <c r="A119" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B119" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.206896551724137+$D$25*0.206896551724137^3),0)</f>
-        <v/>
-      </c>
-      <c r="C119" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.206896551724137+$D$26*0.206896551724137^3),0)</f>
-        <v/>
-      </c>
-      <c r="D119" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.206896551724137+$D$27*0.206896551724137^3),0)</f>
-        <v/>
-      </c>
-      <c r="E119" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.206896551724137+$D$28*0.206896551724137^3),0)</f>
-        <v/>
-      </c>
-      <c r="F119" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.206896551724137+$D$29*0.206896551724137^3),0)</f>
-        <v/>
-      </c>
-      <c r="G119" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.206896551724137+$D$30*0.206896551724137^3),0)</f>
-        <v/>
-      </c>
-      <c r="H119" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.206896551724137+$D$31*0.206896551724137^3),0)</f>
-        <v/>
-      </c>
+      <c r="A119" s="34" t="n"/>
+      <c r="B119" s="34" t="n"/>
+      <c r="C119" s="34" t="n"/>
+      <c r="D119" s="34" t="n"/>
+      <c r="E119" s="34" t="n"/>
+      <c r="F119" s="34" t="n"/>
+      <c r="G119" s="34" t="n"/>
+      <c r="H119" s="34" t="n"/>
     </row>
     <row r="120">
-      <c r="A120" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B120" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.241379310344827+$D$25*0.241379310344827^3),0)</f>
-        <v/>
-      </c>
-      <c r="C120" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.241379310344827+$D$26*0.241379310344827^3),0)</f>
-        <v/>
-      </c>
-      <c r="D120" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.241379310344827+$D$27*0.241379310344827^3),0)</f>
-        <v/>
-      </c>
-      <c r="E120" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.241379310344827+$D$28*0.241379310344827^3),0)</f>
-        <v/>
-      </c>
-      <c r="F120" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.241379310344827+$D$29*0.241379310344827^3),0)</f>
-        <v/>
-      </c>
-      <c r="G120" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.241379310344827+$D$30*0.241379310344827^3),0)</f>
-        <v/>
-      </c>
-      <c r="H120" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.241379310344827+$D$31*0.241379310344827^3),0)</f>
-        <v/>
-      </c>
+      <c r="A120" s="34" t="n"/>
+      <c r="B120" s="34" t="n"/>
+      <c r="C120" s="34" t="n"/>
+      <c r="D120" s="34" t="n"/>
+      <c r="E120" s="34" t="n"/>
+      <c r="F120" s="34" t="n"/>
+      <c r="G120" s="34" t="n"/>
+      <c r="H120" s="34" t="n"/>
     </row>
     <row r="121">
-      <c r="A121" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="B121" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.275862068965517+$D$25*0.275862068965517^3),0)</f>
-        <v/>
-      </c>
-      <c r="C121" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.275862068965517+$D$26*0.275862068965517^3),0)</f>
-        <v/>
-      </c>
-      <c r="D121" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.275862068965517+$D$27*0.275862068965517^3),0)</f>
-        <v/>
-      </c>
-      <c r="E121" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.275862068965517+$D$28*0.275862068965517^3),0)</f>
-        <v/>
-      </c>
-      <c r="F121" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.275862068965517+$D$29*0.275862068965517^3),0)</f>
-        <v/>
-      </c>
-      <c r="G121" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.275862068965517+$D$30*0.275862068965517^3),0)</f>
-        <v/>
-      </c>
-      <c r="H121" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.275862068965517+$D$31*0.275862068965517^3),0)</f>
-        <v/>
-      </c>
+      <c r="A121" s="34" t="n"/>
+      <c r="B121" s="34" t="n"/>
+      <c r="C121" s="34" t="n"/>
+      <c r="D121" s="34" t="n"/>
+      <c r="E121" s="34" t="n"/>
+      <c r="F121" s="34" t="n"/>
+      <c r="G121" s="34" t="n"/>
+      <c r="H121" s="34" t="n"/>
     </row>
     <row r="122">
-      <c r="A122" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="B122" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.310344827586206+$D$25*0.310344827586206^3),0)</f>
-        <v/>
-      </c>
-      <c r="C122" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.310344827586206+$D$26*0.310344827586206^3),0)</f>
-        <v/>
-      </c>
-      <c r="D122" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.310344827586206+$D$27*0.310344827586206^3),0)</f>
-        <v/>
-      </c>
-      <c r="E122" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.310344827586206+$D$28*0.310344827586206^3),0)</f>
-        <v/>
-      </c>
-      <c r="F122" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.310344827586206+$D$29*0.310344827586206^3),0)</f>
-        <v/>
-      </c>
-      <c r="G122" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.310344827586206+$D$30*0.310344827586206^3),0)</f>
-        <v/>
-      </c>
-      <c r="H122" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.310344827586206+$D$31*0.310344827586206^3),0)</f>
-        <v/>
-      </c>
+      <c r="A122" s="34" t="n"/>
+      <c r="B122" s="34" t="n"/>
+      <c r="C122" s="34" t="n"/>
+      <c r="D122" s="34" t="n"/>
+      <c r="E122" s="34" t="n"/>
+      <c r="F122" s="34" t="n"/>
+      <c r="G122" s="34" t="n"/>
+      <c r="H122" s="34" t="n"/>
     </row>
     <row r="123">
-      <c r="A123" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="B123" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.344827586206896+$D$25*0.344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="C123" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.344827586206896+$D$26*0.344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="D123" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.344827586206896+$D$27*0.344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="E123" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.344827586206896+$D$28*0.344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="F123" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.344827586206896+$D$29*0.344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="G123" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.344827586206896+$D$30*0.344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="H123" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.344827586206896+$D$31*0.344827586206896^3),0)</f>
-        <v/>
-      </c>
+      <c r="A123" s="34" t="n"/>
+      <c r="B123" s="34" t="n"/>
+      <c r="C123" s="34" t="n"/>
+      <c r="D123" s="34" t="n"/>
+      <c r="E123" s="34" t="n"/>
+      <c r="F123" s="34" t="n"/>
+      <c r="G123" s="34" t="n"/>
+      <c r="H123" s="34" t="n"/>
     </row>
     <row r="124">
-      <c r="A124" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="B124" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.379310344827586+$D$25*0.379310344827586^3),0)</f>
-        <v/>
-      </c>
-      <c r="C124" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.379310344827586+$D$26*0.379310344827586^3),0)</f>
-        <v/>
-      </c>
-      <c r="D124" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.379310344827586+$D$27*0.379310344827586^3),0)</f>
-        <v/>
-      </c>
-      <c r="E124" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.379310344827586+$D$28*0.379310344827586^3),0)</f>
-        <v/>
-      </c>
-      <c r="F124" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.379310344827586+$D$29*0.379310344827586^3),0)</f>
-        <v/>
-      </c>
-      <c r="G124" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.379310344827586+$D$30*0.379310344827586^3),0)</f>
-        <v/>
-      </c>
-      <c r="H124" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.379310344827586+$D$31*0.379310344827586^3),0)</f>
-        <v/>
-      </c>
+      <c r="A124" s="34" t="n"/>
+      <c r="B124" s="34" t="n"/>
+      <c r="C124" s="34" t="n"/>
+      <c r="D124" s="34" t="n"/>
+      <c r="E124" s="34" t="n"/>
+      <c r="F124" s="34" t="n"/>
+      <c r="G124" s="34" t="n"/>
+      <c r="H124" s="34" t="n"/>
     </row>
     <row r="125">
-      <c r="A125" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B125" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.413793103448275+$D$25*0.413793103448275^3),0)</f>
-        <v/>
-      </c>
-      <c r="C125" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.413793103448275+$D$26*0.413793103448275^3),0)</f>
-        <v/>
-      </c>
-      <c r="D125" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.413793103448275+$D$27*0.413793103448275^3),0)</f>
-        <v/>
-      </c>
-      <c r="E125" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.413793103448275+$D$28*0.413793103448275^3),0)</f>
-        <v/>
-      </c>
-      <c r="F125" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.413793103448275+$D$29*0.413793103448275^3),0)</f>
-        <v/>
-      </c>
-      <c r="G125" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.413793103448275+$D$30*0.413793103448275^3),0)</f>
-        <v/>
-      </c>
-      <c r="H125" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.413793103448275+$D$31*0.413793103448275^3),0)</f>
-        <v/>
-      </c>
+      <c r="A125" s="34" t="n"/>
+      <c r="B125" s="34" t="n"/>
+      <c r="C125" s="34" t="n"/>
+      <c r="D125" s="34" t="n"/>
+      <c r="E125" s="34" t="n"/>
+      <c r="F125" s="34" t="n"/>
+      <c r="G125" s="34" t="n"/>
+      <c r="H125" s="34" t="n"/>
     </row>
     <row r="126">
-      <c r="A126" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B126" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.448275862068965+$D$25*0.448275862068965^3),0)</f>
-        <v/>
-      </c>
-      <c r="C126" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.448275862068965+$D$26*0.448275862068965^3),0)</f>
-        <v/>
-      </c>
-      <c r="D126" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.448275862068965+$D$27*0.448275862068965^3),0)</f>
-        <v/>
-      </c>
-      <c r="E126" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.448275862068965+$D$28*0.448275862068965^3),0)</f>
-        <v/>
-      </c>
-      <c r="F126" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.448275862068965+$D$29*0.448275862068965^3),0)</f>
-        <v/>
-      </c>
-      <c r="G126" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.448275862068965+$D$30*0.448275862068965^3),0)</f>
-        <v/>
-      </c>
-      <c r="H126" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.448275862068965+$D$31*0.448275862068965^3),0)</f>
-        <v/>
-      </c>
+      <c r="A126" s="34" t="n"/>
+      <c r="B126" s="34" t="n"/>
+      <c r="C126" s="34" t="n"/>
+      <c r="D126" s="34" t="n"/>
+      <c r="E126" s="34" t="n"/>
+      <c r="F126" s="34" t="n"/>
+      <c r="G126" s="34" t="n"/>
+      <c r="H126" s="34" t="n"/>
     </row>
     <row r="127">
-      <c r="A127" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B127" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.482758620689655+$D$25*0.482758620689655^3),0)</f>
-        <v/>
-      </c>
-      <c r="C127" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.482758620689655+$D$26*0.482758620689655^3),0)</f>
-        <v/>
-      </c>
-      <c r="D127" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.482758620689655+$D$27*0.482758620689655^3),0)</f>
-        <v/>
-      </c>
-      <c r="E127" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.482758620689655+$D$28*0.482758620689655^3),0)</f>
-        <v/>
-      </c>
-      <c r="F127" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.482758620689655+$D$29*0.482758620689655^3),0)</f>
-        <v/>
-      </c>
-      <c r="G127" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.482758620689655+$D$30*0.482758620689655^3),0)</f>
-        <v/>
-      </c>
-      <c r="H127" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.482758620689655+$D$31*0.482758620689655^3),0)</f>
-        <v/>
-      </c>
+      <c r="A127" s="34" t="n"/>
+      <c r="B127" s="34" t="n"/>
+      <c r="C127" s="34" t="n"/>
+      <c r="D127" s="34" t="n"/>
+      <c r="E127" s="34" t="n"/>
+      <c r="F127" s="34" t="n"/>
+      <c r="G127" s="34" t="n"/>
+      <c r="H127" s="34" t="n"/>
     </row>
     <row r="128">
-      <c r="A128" s="16" t="n">
-        <v>16</v>
-      </c>
-      <c r="B128" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.517241379310344+$D$25*0.517241379310344^3),0)</f>
-        <v/>
-      </c>
-      <c r="C128" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.517241379310344+$D$26*0.517241379310344^3),0)</f>
-        <v/>
-      </c>
-      <c r="D128" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.517241379310344+$D$27*0.517241379310344^3),0)</f>
-        <v/>
-      </c>
-      <c r="E128" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.517241379310344+$D$28*0.517241379310344^3),0)</f>
-        <v/>
-      </c>
-      <c r="F128" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.517241379310344+$D$29*0.517241379310344^3),0)</f>
-        <v/>
-      </c>
-      <c r="G128" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.517241379310344+$D$30*0.517241379310344^3),0)</f>
-        <v/>
-      </c>
-      <c r="H128" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.517241379310344+$D$31*0.517241379310344^3),0)</f>
-        <v/>
-      </c>
+      <c r="A128" s="34" t="n"/>
+      <c r="B128" s="34" t="n"/>
+      <c r="C128" s="34" t="n"/>
+      <c r="D128" s="34" t="n"/>
+      <c r="E128" s="34" t="n"/>
+      <c r="F128" s="34" t="n"/>
+      <c r="G128" s="34" t="n"/>
+      <c r="H128" s="34" t="n"/>
     </row>
     <row r="129">
-      <c r="A129" s="16" t="n">
-        <v>17</v>
-      </c>
-      <c r="B129" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.551724137931034+$D$25*0.551724137931034^3),0)</f>
-        <v/>
-      </c>
-      <c r="C129" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.551724137931034+$D$26*0.551724137931034^3),0)</f>
-        <v/>
-      </c>
-      <c r="D129" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.551724137931034+$D$27*0.551724137931034^3),0)</f>
-        <v/>
-      </c>
-      <c r="E129" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.551724137931034+$D$28*0.551724137931034^3),0)</f>
-        <v/>
-      </c>
-      <c r="F129" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.551724137931034+$D$29*0.551724137931034^3),0)</f>
-        <v/>
-      </c>
-      <c r="G129" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.551724137931034+$D$30*0.551724137931034^3),0)</f>
-        <v/>
-      </c>
-      <c r="H129" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.551724137931034+$D$31*0.551724137931034^3),0)</f>
-        <v/>
-      </c>
+      <c r="A129" s="34" t="n"/>
+      <c r="B129" s="34" t="n"/>
+      <c r="C129" s="34" t="n"/>
+      <c r="D129" s="34" t="n"/>
+      <c r="E129" s="34" t="n"/>
+      <c r="F129" s="34" t="n"/>
+      <c r="G129" s="34" t="n"/>
+      <c r="H129" s="34" t="n"/>
     </row>
     <row r="130">
-      <c r="A130" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="B130" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.586206896551724+$D$25*0.586206896551724^3),0)</f>
-        <v/>
-      </c>
-      <c r="C130" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.586206896551724+$D$26*0.586206896551724^3),0)</f>
-        <v/>
-      </c>
-      <c r="D130" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.586206896551724+$D$27*0.586206896551724^3),0)</f>
-        <v/>
-      </c>
-      <c r="E130" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.586206896551724+$D$28*0.586206896551724^3),0)</f>
-        <v/>
-      </c>
-      <c r="F130" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.586206896551724+$D$29*0.586206896551724^3),0)</f>
-        <v/>
-      </c>
-      <c r="G130" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.586206896551724+$D$30*0.586206896551724^3),0)</f>
-        <v/>
-      </c>
-      <c r="H130" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.586206896551724+$D$31*0.586206896551724^3),0)</f>
-        <v/>
-      </c>
+      <c r="A130" s="34" t="n"/>
+      <c r="B130" s="34" t="n"/>
+      <c r="C130" s="34" t="n"/>
+      <c r="D130" s="34" t="n"/>
+      <c r="E130" s="34" t="n"/>
+      <c r="F130" s="34" t="n"/>
+      <c r="G130" s="34" t="n"/>
+      <c r="H130" s="34" t="n"/>
     </row>
     <row r="131">
-      <c r="A131" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="B131" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.620689655172413+$D$25*0.620689655172413^3),0)</f>
-        <v/>
-      </c>
-      <c r="C131" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.620689655172413+$D$26*0.620689655172413^3),0)</f>
-        <v/>
-      </c>
-      <c r="D131" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.620689655172413+$D$27*0.620689655172413^3),0)</f>
-        <v/>
-      </c>
-      <c r="E131" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.620689655172413+$D$28*0.620689655172413^3),0)</f>
-        <v/>
-      </c>
-      <c r="F131" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.620689655172413+$D$29*0.620689655172413^3),0)</f>
-        <v/>
-      </c>
-      <c r="G131" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.620689655172413+$D$30*0.620689655172413^3),0)</f>
-        <v/>
-      </c>
-      <c r="H131" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.620689655172413+$D$31*0.620689655172413^3),0)</f>
-        <v/>
-      </c>
+      <c r="A131" s="34" t="n"/>
+      <c r="B131" s="34" t="n"/>
+      <c r="C131" s="34" t="n"/>
+      <c r="D131" s="34" t="n"/>
+      <c r="E131" s="34" t="n"/>
+      <c r="F131" s="34" t="n"/>
+      <c r="G131" s="34" t="n"/>
+      <c r="H131" s="34" t="n"/>
     </row>
     <row r="132">
-      <c r="A132" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="B132" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.655172413793103+$D$25*0.655172413793103^3),0)</f>
-        <v/>
-      </c>
-      <c r="C132" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.655172413793103+$D$26*0.655172413793103^3),0)</f>
-        <v/>
-      </c>
-      <c r="D132" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.655172413793103+$D$27*0.655172413793103^3),0)</f>
-        <v/>
-      </c>
-      <c r="E132" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.655172413793103+$D$28*0.655172413793103^3),0)</f>
-        <v/>
-      </c>
-      <c r="F132" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.655172413793103+$D$29*0.655172413793103^3),0)</f>
-        <v/>
-      </c>
-      <c r="G132" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.655172413793103+$D$30*0.655172413793103^3),0)</f>
-        <v/>
-      </c>
-      <c r="H132" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.655172413793103+$D$31*0.655172413793103^3),0)</f>
-        <v/>
-      </c>
+      <c r="A132" s="34" t="n"/>
+      <c r="B132" s="34" t="n"/>
+      <c r="C132" s="34" t="n"/>
+      <c r="D132" s="34" t="n"/>
+      <c r="E132" s="34" t="n"/>
+      <c r="F132" s="34" t="n"/>
+      <c r="G132" s="34" t="n"/>
+      <c r="H132" s="34" t="n"/>
     </row>
     <row r="133">
-      <c r="A133" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="B133" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.689655172413793+$D$25*0.689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="C133" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.689655172413793+$D$26*0.689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="D133" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.689655172413793+$D$27*0.689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="E133" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.689655172413793+$D$28*0.689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="F133" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.689655172413793+$D$29*0.689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="G133" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.689655172413793+$D$30*0.689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="H133" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.689655172413793+$D$31*0.689655172413793^3),0)</f>
-        <v/>
-      </c>
+      <c r="A133" s="34" t="n"/>
+      <c r="B133" s="34" t="n"/>
+      <c r="C133" s="34" t="n"/>
+      <c r="D133" s="34" t="n"/>
+      <c r="E133" s="34" t="n"/>
+      <c r="F133" s="34" t="n"/>
+      <c r="G133" s="34" t="n"/>
+      <c r="H133" s="34" t="n"/>
     </row>
     <row r="134">
-      <c r="A134" s="16" t="n">
-        <v>22</v>
-      </c>
-      <c r="B134" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.724137931034482+$D$25*0.724137931034482^3),0)</f>
-        <v/>
-      </c>
-      <c r="C134" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.724137931034482+$D$26*0.724137931034482^3),0)</f>
-        <v/>
-      </c>
-      <c r="D134" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.724137931034482+$D$27*0.724137931034482^3),0)</f>
-        <v/>
-      </c>
-      <c r="E134" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.724137931034482+$D$28*0.724137931034482^3),0)</f>
-        <v/>
-      </c>
-      <c r="F134" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.724137931034482+$D$29*0.724137931034482^3),0)</f>
-        <v/>
-      </c>
-      <c r="G134" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.724137931034482+$D$30*0.724137931034482^3),0)</f>
-        <v/>
-      </c>
-      <c r="H134" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.724137931034482+$D$31*0.724137931034482^3),0)</f>
-        <v/>
-      </c>
+      <c r="A134" s="34" t="n"/>
+      <c r="B134" s="34" t="n"/>
+      <c r="C134" s="34" t="n"/>
+      <c r="D134" s="34" t="n"/>
+      <c r="E134" s="34" t="n"/>
+      <c r="F134" s="34" t="n"/>
+      <c r="G134" s="34" t="n"/>
+      <c r="H134" s="34" t="n"/>
     </row>
     <row r="135">
-      <c r="A135" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="B135" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.758620689655172+$D$25*0.758620689655172^3),0)</f>
-        <v/>
-      </c>
-      <c r="C135" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.758620689655172+$D$26*0.758620689655172^3),0)</f>
-        <v/>
-      </c>
-      <c r="D135" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.758620689655172+$D$27*0.758620689655172^3),0)</f>
-        <v/>
-      </c>
-      <c r="E135" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.758620689655172+$D$28*0.758620689655172^3),0)</f>
-        <v/>
-      </c>
-      <c r="F135" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.758620689655172+$D$29*0.758620689655172^3),0)</f>
-        <v/>
-      </c>
-      <c r="G135" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.758620689655172+$D$30*0.758620689655172^3),0)</f>
-        <v/>
-      </c>
-      <c r="H135" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.758620689655172+$D$31*0.758620689655172^3),0)</f>
-        <v/>
-      </c>
+      <c r="A135" s="34" t="n"/>
+      <c r="B135" s="34" t="n"/>
+      <c r="C135" s="34" t="n"/>
+      <c r="D135" s="34" t="n"/>
+      <c r="E135" s="34" t="n"/>
+      <c r="F135" s="34" t="n"/>
+      <c r="G135" s="34" t="n"/>
+      <c r="H135" s="34" t="n"/>
     </row>
     <row r="136">
-      <c r="A136" s="16" t="n">
-        <v>24</v>
-      </c>
-      <c r="B136" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.793103448275862+$D$25*0.793103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="C136" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.793103448275862+$D$26*0.793103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="D136" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.793103448275862+$D$27*0.793103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="E136" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.793103448275862+$D$28*0.793103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="F136" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.793103448275862+$D$29*0.793103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="G136" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.793103448275862+$D$30*0.793103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="H136" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.793103448275862+$D$31*0.793103448275862^3),0)</f>
-        <v/>
-      </c>
+      <c r="A136" s="34" t="n"/>
+      <c r="B136" s="34" t="n"/>
+      <c r="C136" s="34" t="n"/>
+      <c r="D136" s="34" t="n"/>
+      <c r="E136" s="34" t="n"/>
+      <c r="F136" s="34" t="n"/>
+      <c r="G136" s="34" t="n"/>
+      <c r="H136" s="34" t="n"/>
     </row>
     <row r="137">
-      <c r="A137" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="B137" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.827586206896551+$D$25*0.827586206896551^3),0)</f>
-        <v/>
-      </c>
-      <c r="C137" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.827586206896551+$D$26*0.827586206896551^3),0)</f>
-        <v/>
-      </c>
-      <c r="D137" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.827586206896551+$D$27*0.827586206896551^3),0)</f>
-        <v/>
-      </c>
-      <c r="E137" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.827586206896551+$D$28*0.827586206896551^3),0)</f>
-        <v/>
-      </c>
-      <c r="F137" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.827586206896551+$D$29*0.827586206896551^3),0)</f>
-        <v/>
-      </c>
-      <c r="G137" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.827586206896551+$D$30*0.827586206896551^3),0)</f>
-        <v/>
-      </c>
-      <c r="H137" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.827586206896551+$D$31*0.827586206896551^3),0)</f>
-        <v/>
-      </c>
+      <c r="A137" s="34" t="n"/>
+      <c r="B137" s="34" t="n"/>
+      <c r="C137" s="34" t="n"/>
+      <c r="D137" s="34" t="n"/>
+      <c r="E137" s="34" t="n"/>
+      <c r="F137" s="34" t="n"/>
+      <c r="G137" s="34" t="n"/>
+      <c r="H137" s="34" t="n"/>
     </row>
     <row r="138">
-      <c r="A138" s="16" t="n">
-        <v>26</v>
-      </c>
-      <c r="B138" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.862068965517241+$D$25*0.862068965517241^3),0)</f>
-        <v/>
-      </c>
-      <c r="C138" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.862068965517241+$D$26*0.862068965517241^3),0)</f>
-        <v/>
-      </c>
-      <c r="D138" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.862068965517241+$D$27*0.862068965517241^3),0)</f>
-        <v/>
-      </c>
-      <c r="E138" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.862068965517241+$D$28*0.862068965517241^3),0)</f>
-        <v/>
-      </c>
-      <c r="F138" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.862068965517241+$D$29*0.862068965517241^3),0)</f>
-        <v/>
-      </c>
-      <c r="G138" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.862068965517241+$D$30*0.862068965517241^3),0)</f>
-        <v/>
-      </c>
-      <c r="H138" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.862068965517241+$D$31*0.862068965517241^3),0)</f>
-        <v/>
-      </c>
+      <c r="A138" s="34" t="n"/>
+      <c r="B138" s="34" t="n"/>
+      <c r="C138" s="34" t="n"/>
+      <c r="D138" s="34" t="n"/>
+      <c r="E138" s="34" t="n"/>
+      <c r="F138" s="34" t="n"/>
+      <c r="G138" s="34" t="n"/>
+      <c r="H138" s="34" t="n"/>
     </row>
     <row r="139">
-      <c r="A139" s="16" t="n">
-        <v>27</v>
-      </c>
-      <c r="B139" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.896551724137931+$D$25*0.896551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="C139" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.896551724137931+$D$26*0.896551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="D139" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.896551724137931+$D$27*0.896551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="E139" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.896551724137931+$D$28*0.896551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="F139" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.896551724137931+$D$29*0.896551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="G139" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.896551724137931+$D$30*0.896551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="H139" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.896551724137931+$D$31*0.896551724137931^3),0)</f>
-        <v/>
-      </c>
+      <c r="A139" s="34" t="n"/>
+      <c r="B139" s="34" t="n"/>
+      <c r="C139" s="34" t="n"/>
+      <c r="D139" s="34" t="n"/>
+      <c r="E139" s="34" t="n"/>
+      <c r="F139" s="34" t="n"/>
+      <c r="G139" s="34" t="n"/>
+      <c r="H139" s="34" t="n"/>
     </row>
     <row r="140">
-      <c r="A140" s="16" t="n">
-        <v>28</v>
-      </c>
-      <c r="B140" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.93103448275862+$D$25*0.93103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="C140" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.93103448275862+$D$26*0.93103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="D140" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.93103448275862+$D$27*0.93103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="E140" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.93103448275862+$D$28*0.93103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="F140" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.93103448275862+$D$29*0.93103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="G140" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.93103448275862+$D$30*0.93103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="H140" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.93103448275862+$D$31*0.93103448275862^3),0)</f>
-        <v/>
-      </c>
+      <c r="A140" s="34" t="n"/>
+      <c r="B140" s="34" t="n"/>
+      <c r="C140" s="34" t="n"/>
+      <c r="D140" s="34" t="n"/>
+      <c r="E140" s="34" t="n"/>
+      <c r="F140" s="34" t="n"/>
+      <c r="G140" s="34" t="n"/>
+      <c r="H140" s="34" t="n"/>
     </row>
     <row r="141">
-      <c r="A141" s="16" t="n">
-        <v>29</v>
-      </c>
-      <c r="B141" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*0.96551724137931+$D$25*0.96551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="C141" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*0.96551724137931+$D$26*0.96551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="D141" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*0.96551724137931+$D$27*0.96551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="E141" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*0.96551724137931+$D$28*0.96551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="F141" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*0.96551724137931+$D$29*0.96551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="G141" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*0.96551724137931+$D$30*0.96551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="H141" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*0.96551724137931+$D$31*0.96551724137931^3),0)</f>
-        <v/>
-      </c>
+      <c r="A141" s="34" t="n"/>
+      <c r="B141" s="34" t="n"/>
+      <c r="C141" s="34" t="n"/>
+      <c r="D141" s="34" t="n"/>
+      <c r="E141" s="34" t="n"/>
+      <c r="F141" s="34" t="n"/>
+      <c r="G141" s="34" t="n"/>
+      <c r="H141" s="34" t="n"/>
     </row>
     <row r="142">
-      <c r="A142" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="B142" s="16">
-        <f>ROUND($B$25+($C$25-$B$25)*((1-$D$25)*1+$D$25*1^3),0)</f>
-        <v/>
-      </c>
-      <c r="C142" s="16">
-        <f>ROUND($B$26+($C$26-$B$26)*((1-$D$26)*1+$D$26*1^3),0)</f>
-        <v/>
-      </c>
-      <c r="D142" s="16">
-        <f>ROUND($B$27+($C$27-$B$27)*((1-$D$27)*1+$D$27*1^3),0)</f>
-        <v/>
-      </c>
-      <c r="E142" s="16">
-        <f>ROUND($B$28+($C$28-$B$28)*((1-$D$28)*1+$D$28*1^3),0)</f>
-        <v/>
-      </c>
-      <c r="F142" s="16">
-        <f>ROUND($B$29+($C$29-$B$29)*((1-$D$29)*1+$D$29*1^3),0)</f>
-        <v/>
-      </c>
-      <c r="G142" s="16">
-        <f>ROUND($B$30+($C$30-$B$30)*((1-$D$30)*1+$D$30*1^3),0)</f>
-        <v/>
-      </c>
-      <c r="H142" s="16">
-        <f>ROUND($B$31+($C$31-$B$31)*((1-$D$31)*1+$D$31*1^3),0)</f>
-        <v/>
-      </c>
+      <c r="A142" s="34" t="n"/>
+      <c r="B142" s="34" t="n"/>
+      <c r="C142" s="34" t="n"/>
+      <c r="D142" s="34" t="n"/>
+      <c r="E142" s="34" t="n"/>
+      <c r="F142" s="34" t="n"/>
+      <c r="G142" s="34" t="n"/>
+      <c r="H142" s="34" t="n"/>
+    </row>
+    <row r="143">
+      <c r="A143" s="34" t="n"/>
+      <c r="B143" s="34" t="n"/>
+      <c r="C143" s="34" t="n"/>
+      <c r="D143" s="34" t="n"/>
+      <c r="E143" s="34" t="n"/>
+      <c r="F143" s="34" t="n"/>
+      <c r="G143" s="34" t="n"/>
+      <c r="H143" s="34" t="n"/>
     </row>
     <row r="144">
-      <c r="A144" s="28" t="inlineStr">
-        <is>
-          <t>[마법딜러·힐러 (가칭)] 레벨 1~30 스탯 (자동 계산)</t>
-        </is>
-      </c>
+      <c r="A144" s="34" t="n"/>
+      <c r="B144" s="34" t="n"/>
+      <c r="C144" s="34" t="n"/>
+      <c r="D144" s="34" t="n"/>
+      <c r="E144" s="34" t="n"/>
+      <c r="F144" s="34" t="n"/>
+      <c r="G144" s="34" t="n"/>
+      <c r="H144" s="34" t="n"/>
     </row>
     <row r="145" ht="18" customHeight="1" s="24">
-      <c r="A145" s="14" t="inlineStr">
-        <is>
-          <t>레벨</t>
-        </is>
-      </c>
-      <c r="B145" s="14" t="inlineStr">
-        <is>
-          <t>HP</t>
-        </is>
-      </c>
-      <c r="C145" s="14" t="inlineStr">
-        <is>
-          <t>ATK</t>
-        </is>
-      </c>
-      <c r="D145" s="14" t="inlineStr">
-        <is>
-          <t>DEF</t>
-        </is>
-      </c>
-      <c r="E145" s="14" t="inlineStr">
-        <is>
-          <t>속도</t>
-        </is>
-      </c>
-      <c r="F145" s="14" t="inlineStr">
-        <is>
-          <t>힘</t>
-        </is>
-      </c>
-      <c r="G145" s="14" t="inlineStr">
-        <is>
-          <t>지력</t>
-        </is>
-      </c>
-      <c r="H145" s="14" t="inlineStr">
-        <is>
-          <t>치료효율</t>
-        </is>
-      </c>
+      <c r="A145" s="34" t="n"/>
+      <c r="B145" s="34" t="n"/>
+      <c r="C145" s="34" t="n"/>
+      <c r="D145" s="34" t="n"/>
+      <c r="E145" s="34" t="n"/>
+      <c r="F145" s="34" t="n"/>
+      <c r="G145" s="34" t="n"/>
+      <c r="H145" s="34" t="n"/>
     </row>
     <row r="146">
-      <c r="A146" s="16" t="n">
-        <v>1</v>
-      </c>
-      <c r="B146" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0+$D$36*0^3),0)</f>
-        <v/>
-      </c>
-      <c r="C146" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0+$D$37*0^3),0)</f>
-        <v/>
-      </c>
-      <c r="D146" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0+$D$38*0^3),0)</f>
-        <v/>
-      </c>
-      <c r="E146" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0+$D$39*0^3),0)</f>
-        <v/>
-      </c>
-      <c r="F146" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0+$D$40*0^3),0)</f>
-        <v/>
-      </c>
-      <c r="G146" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0+$D$41*0^3),0)</f>
-        <v/>
-      </c>
-      <c r="H146" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0+$D$42*0^3),0)</f>
-        <v/>
-      </c>
+      <c r="A146" s="34" t="n"/>
+      <c r="B146" s="34" t="n"/>
+      <c r="C146" s="34" t="n"/>
+      <c r="D146" s="34" t="n"/>
+      <c r="E146" s="34" t="n"/>
+      <c r="F146" s="34" t="n"/>
+      <c r="G146" s="34" t="n"/>
+      <c r="H146" s="34" t="n"/>
     </row>
     <row r="147">
-      <c r="A147" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B147" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.0344827586206896+$D$36*0.0344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="C147" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.0344827586206896+$D$37*0.0344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="D147" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.0344827586206896+$D$38*0.0344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="E147" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.0344827586206896+$D$39*0.0344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="F147" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.0344827586206896+$D$40*0.0344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="G147" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.0344827586206896+$D$41*0.0344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="H147" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.0344827586206896+$D$42*0.0344827586206896^3),0)</f>
-        <v/>
-      </c>
+      <c r="A147" s="34" t="n"/>
+      <c r="B147" s="34" t="n"/>
+      <c r="C147" s="34" t="n"/>
+      <c r="D147" s="34" t="n"/>
+      <c r="E147" s="34" t="n"/>
+      <c r="F147" s="34" t="n"/>
+      <c r="G147" s="34" t="n"/>
+      <c r="H147" s="34" t="n"/>
     </row>
     <row r="148">
-      <c r="A148" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B148" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.0689655172413793+$D$36*0.0689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="C148" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.0689655172413793+$D$37*0.0689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="D148" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.0689655172413793+$D$38*0.0689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="E148" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.0689655172413793+$D$39*0.0689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="F148" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.0689655172413793+$D$40*0.0689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="G148" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.0689655172413793+$D$41*0.0689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="H148" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.0689655172413793+$D$42*0.0689655172413793^3),0)</f>
-        <v/>
-      </c>
+      <c r="A148" s="34" t="n"/>
+      <c r="B148" s="34" t="n"/>
+      <c r="C148" s="34" t="n"/>
+      <c r="D148" s="34" t="n"/>
+      <c r="E148" s="34" t="n"/>
+      <c r="F148" s="34" t="n"/>
+      <c r="G148" s="34" t="n"/>
+      <c r="H148" s="34" t="n"/>
     </row>
     <row r="149">
-      <c r="A149" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B149" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.103448275862068+$D$36*0.103448275862068^3),0)</f>
-        <v/>
-      </c>
-      <c r="C149" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.103448275862068+$D$37*0.103448275862068^3),0)</f>
-        <v/>
-      </c>
-      <c r="D149" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.103448275862068+$D$38*0.103448275862068^3),0)</f>
-        <v/>
-      </c>
-      <c r="E149" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.103448275862068+$D$39*0.103448275862068^3),0)</f>
-        <v/>
-      </c>
-      <c r="F149" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.103448275862068+$D$40*0.103448275862068^3),0)</f>
-        <v/>
-      </c>
-      <c r="G149" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.103448275862068+$D$41*0.103448275862068^3),0)</f>
-        <v/>
-      </c>
-      <c r="H149" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.103448275862068+$D$42*0.103448275862068^3),0)</f>
-        <v/>
-      </c>
+      <c r="A149" s="34" t="n"/>
+      <c r="B149" s="34" t="n"/>
+      <c r="C149" s="34" t="n"/>
+      <c r="D149" s="34" t="n"/>
+      <c r="E149" s="34" t="n"/>
+      <c r="F149" s="34" t="n"/>
+      <c r="G149" s="34" t="n"/>
+      <c r="H149" s="34" t="n"/>
     </row>
     <row r="150">
-      <c r="A150" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B150" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.137931034482758+$D$36*0.137931034482758^3),0)</f>
-        <v/>
-      </c>
-      <c r="C150" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.137931034482758+$D$37*0.137931034482758^3),0)</f>
-        <v/>
-      </c>
-      <c r="D150" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.137931034482758+$D$38*0.137931034482758^3),0)</f>
-        <v/>
-      </c>
-      <c r="E150" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.137931034482758+$D$39*0.137931034482758^3),0)</f>
-        <v/>
-      </c>
-      <c r="F150" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.137931034482758+$D$40*0.137931034482758^3),0)</f>
-        <v/>
-      </c>
-      <c r="G150" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.137931034482758+$D$41*0.137931034482758^3),0)</f>
-        <v/>
-      </c>
-      <c r="H150" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.137931034482758+$D$42*0.137931034482758^3),0)</f>
-        <v/>
-      </c>
+      <c r="A150" s="34" t="n"/>
+      <c r="B150" s="34" t="n"/>
+      <c r="C150" s="34" t="n"/>
+      <c r="D150" s="34" t="n"/>
+      <c r="E150" s="34" t="n"/>
+      <c r="F150" s="34" t="n"/>
+      <c r="G150" s="34" t="n"/>
+      <c r="H150" s="34" t="n"/>
     </row>
     <row r="151">
-      <c r="A151" s="16" t="n">
-        <v>6</v>
-      </c>
-      <c r="B151" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.172413793103448+$D$36*0.172413793103448^3),0)</f>
-        <v/>
-      </c>
-      <c r="C151" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.172413793103448+$D$37*0.172413793103448^3),0)</f>
-        <v/>
-      </c>
-      <c r="D151" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.172413793103448+$D$38*0.172413793103448^3),0)</f>
-        <v/>
-      </c>
-      <c r="E151" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.172413793103448+$D$39*0.172413793103448^3),0)</f>
-        <v/>
-      </c>
-      <c r="F151" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.172413793103448+$D$40*0.172413793103448^3),0)</f>
-        <v/>
-      </c>
-      <c r="G151" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.172413793103448+$D$41*0.172413793103448^3),0)</f>
-        <v/>
-      </c>
-      <c r="H151" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.172413793103448+$D$42*0.172413793103448^3),0)</f>
-        <v/>
-      </c>
+      <c r="A151" s="34" t="n"/>
+      <c r="B151" s="34" t="n"/>
+      <c r="C151" s="34" t="n"/>
+      <c r="D151" s="34" t="n"/>
+      <c r="E151" s="34" t="n"/>
+      <c r="F151" s="34" t="n"/>
+      <c r="G151" s="34" t="n"/>
+      <c r="H151" s="34" t="n"/>
     </row>
     <row r="152">
-      <c r="A152" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B152" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.206896551724137+$D$36*0.206896551724137^3),0)</f>
-        <v/>
-      </c>
-      <c r="C152" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.206896551724137+$D$37*0.206896551724137^3),0)</f>
-        <v/>
-      </c>
-      <c r="D152" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.206896551724137+$D$38*0.206896551724137^3),0)</f>
-        <v/>
-      </c>
-      <c r="E152" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.206896551724137+$D$39*0.206896551724137^3),0)</f>
-        <v/>
-      </c>
-      <c r="F152" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.206896551724137+$D$40*0.206896551724137^3),0)</f>
-        <v/>
-      </c>
-      <c r="G152" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.206896551724137+$D$41*0.206896551724137^3),0)</f>
-        <v/>
-      </c>
-      <c r="H152" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.206896551724137+$D$42*0.206896551724137^3),0)</f>
-        <v/>
-      </c>
+      <c r="A152" s="34" t="n"/>
+      <c r="B152" s="34" t="n"/>
+      <c r="C152" s="34" t="n"/>
+      <c r="D152" s="34" t="n"/>
+      <c r="E152" s="34" t="n"/>
+      <c r="F152" s="34" t="n"/>
+      <c r="G152" s="34" t="n"/>
+      <c r="H152" s="34" t="n"/>
     </row>
     <row r="153">
-      <c r="A153" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B153" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.241379310344827+$D$36*0.241379310344827^3),0)</f>
-        <v/>
-      </c>
-      <c r="C153" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.241379310344827+$D$37*0.241379310344827^3),0)</f>
-        <v/>
-      </c>
-      <c r="D153" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.241379310344827+$D$38*0.241379310344827^3),0)</f>
-        <v/>
-      </c>
-      <c r="E153" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.241379310344827+$D$39*0.241379310344827^3),0)</f>
-        <v/>
-      </c>
-      <c r="F153" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.241379310344827+$D$40*0.241379310344827^3),0)</f>
-        <v/>
-      </c>
-      <c r="G153" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.241379310344827+$D$41*0.241379310344827^3),0)</f>
-        <v/>
-      </c>
-      <c r="H153" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.241379310344827+$D$42*0.241379310344827^3),0)</f>
-        <v/>
-      </c>
+      <c r="A153" s="34" t="n"/>
+      <c r="B153" s="34" t="n"/>
+      <c r="C153" s="34" t="n"/>
+      <c r="D153" s="34" t="n"/>
+      <c r="E153" s="34" t="n"/>
+      <c r="F153" s="34" t="n"/>
+      <c r="G153" s="34" t="n"/>
+      <c r="H153" s="34" t="n"/>
     </row>
     <row r="154">
-      <c r="A154" s="16" t="n">
-        <v>9</v>
-      </c>
-      <c r="B154" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.275862068965517+$D$36*0.275862068965517^3),0)</f>
-        <v/>
-      </c>
-      <c r="C154" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.275862068965517+$D$37*0.275862068965517^3),0)</f>
-        <v/>
-      </c>
-      <c r="D154" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.275862068965517+$D$38*0.275862068965517^3),0)</f>
-        <v/>
-      </c>
-      <c r="E154" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.275862068965517+$D$39*0.275862068965517^3),0)</f>
-        <v/>
-      </c>
-      <c r="F154" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.275862068965517+$D$40*0.275862068965517^3),0)</f>
-        <v/>
-      </c>
-      <c r="G154" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.275862068965517+$D$41*0.275862068965517^3),0)</f>
-        <v/>
-      </c>
-      <c r="H154" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.275862068965517+$D$42*0.275862068965517^3),0)</f>
-        <v/>
-      </c>
+      <c r="A154" s="34" t="n"/>
+      <c r="B154" s="34" t="n"/>
+      <c r="C154" s="34" t="n"/>
+      <c r="D154" s="34" t="n"/>
+      <c r="E154" s="34" t="n"/>
+      <c r="F154" s="34" t="n"/>
+      <c r="G154" s="34" t="n"/>
+      <c r="H154" s="34" t="n"/>
     </row>
     <row r="155">
-      <c r="A155" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="B155" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.310344827586206+$D$36*0.310344827586206^3),0)</f>
-        <v/>
-      </c>
-      <c r="C155" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.310344827586206+$D$37*0.310344827586206^3),0)</f>
-        <v/>
-      </c>
-      <c r="D155" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.310344827586206+$D$38*0.310344827586206^3),0)</f>
-        <v/>
-      </c>
-      <c r="E155" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.310344827586206+$D$39*0.310344827586206^3),0)</f>
-        <v/>
-      </c>
-      <c r="F155" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.310344827586206+$D$40*0.310344827586206^3),0)</f>
-        <v/>
-      </c>
-      <c r="G155" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.310344827586206+$D$41*0.310344827586206^3),0)</f>
-        <v/>
-      </c>
-      <c r="H155" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.310344827586206+$D$42*0.310344827586206^3),0)</f>
-        <v/>
-      </c>
+      <c r="A155" s="34" t="n"/>
+      <c r="B155" s="34" t="n"/>
+      <c r="C155" s="34" t="n"/>
+      <c r="D155" s="34" t="n"/>
+      <c r="E155" s="34" t="n"/>
+      <c r="F155" s="34" t="n"/>
+      <c r="G155" s="34" t="n"/>
+      <c r="H155" s="34" t="n"/>
     </row>
     <row r="156">
-      <c r="A156" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="B156" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.344827586206896+$D$36*0.344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="C156" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.344827586206896+$D$37*0.344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="D156" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.344827586206896+$D$38*0.344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="E156" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.344827586206896+$D$39*0.344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="F156" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.344827586206896+$D$40*0.344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="G156" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.344827586206896+$D$41*0.344827586206896^3),0)</f>
-        <v/>
-      </c>
-      <c r="H156" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.344827586206896+$D$42*0.344827586206896^3),0)</f>
-        <v/>
-      </c>
+      <c r="A156" s="34" t="n"/>
+      <c r="B156" s="34" t="n"/>
+      <c r="C156" s="34" t="n"/>
+      <c r="D156" s="34" t="n"/>
+      <c r="E156" s="34" t="n"/>
+      <c r="F156" s="34" t="n"/>
+      <c r="G156" s="34" t="n"/>
+      <c r="H156" s="34" t="n"/>
     </row>
     <row r="157">
-      <c r="A157" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="B157" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.379310344827586+$D$36*0.379310344827586^3),0)</f>
-        <v/>
-      </c>
-      <c r="C157" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.379310344827586+$D$37*0.379310344827586^3),0)</f>
-        <v/>
-      </c>
-      <c r="D157" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.379310344827586+$D$38*0.379310344827586^3),0)</f>
-        <v/>
-      </c>
-      <c r="E157" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.379310344827586+$D$39*0.379310344827586^3),0)</f>
-        <v/>
-      </c>
-      <c r="F157" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.379310344827586+$D$40*0.379310344827586^3),0)</f>
-        <v/>
-      </c>
-      <c r="G157" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.379310344827586+$D$41*0.379310344827586^3),0)</f>
-        <v/>
-      </c>
-      <c r="H157" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.379310344827586+$D$42*0.379310344827586^3),0)</f>
-        <v/>
-      </c>
+      <c r="A157" s="34" t="n"/>
+      <c r="B157" s="34" t="n"/>
+      <c r="C157" s="34" t="n"/>
+      <c r="D157" s="34" t="n"/>
+      <c r="E157" s="34" t="n"/>
+      <c r="F157" s="34" t="n"/>
+      <c r="G157" s="34" t="n"/>
+      <c r="H157" s="34" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="16" t="n">
-        <v>13</v>
-      </c>
-      <c r="B158" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.413793103448275+$D$36*0.413793103448275^3),0)</f>
-        <v/>
-      </c>
-      <c r="C158" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.413793103448275+$D$37*0.413793103448275^3),0)</f>
-        <v/>
-      </c>
-      <c r="D158" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.413793103448275+$D$38*0.413793103448275^3),0)</f>
-        <v/>
-      </c>
-      <c r="E158" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.413793103448275+$D$39*0.413793103448275^3),0)</f>
-        <v/>
-      </c>
-      <c r="F158" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.413793103448275+$D$40*0.413793103448275^3),0)</f>
-        <v/>
-      </c>
-      <c r="G158" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.413793103448275+$D$41*0.413793103448275^3),0)</f>
-        <v/>
-      </c>
-      <c r="H158" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.413793103448275+$D$42*0.413793103448275^3),0)</f>
-        <v/>
-      </c>
+      <c r="A158" s="34" t="n"/>
+      <c r="B158" s="34" t="n"/>
+      <c r="C158" s="34" t="n"/>
+      <c r="D158" s="34" t="n"/>
+      <c r="E158" s="34" t="n"/>
+      <c r="F158" s="34" t="n"/>
+      <c r="G158" s="34" t="n"/>
+      <c r="H158" s="34" t="n"/>
     </row>
     <row r="159">
-      <c r="A159" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B159" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.448275862068965+$D$36*0.448275862068965^3),0)</f>
-        <v/>
-      </c>
-      <c r="C159" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.448275862068965+$D$37*0.448275862068965^3),0)</f>
-        <v/>
-      </c>
-      <c r="D159" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.448275862068965+$D$38*0.448275862068965^3),0)</f>
-        <v/>
-      </c>
-      <c r="E159" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.448275862068965+$D$39*0.448275862068965^3),0)</f>
-        <v/>
-      </c>
-      <c r="F159" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.448275862068965+$D$40*0.448275862068965^3),0)</f>
-        <v/>
-      </c>
-      <c r="G159" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.448275862068965+$D$41*0.448275862068965^3),0)</f>
-        <v/>
-      </c>
-      <c r="H159" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.448275862068965+$D$42*0.448275862068965^3),0)</f>
-        <v/>
-      </c>
+      <c r="A159" s="34" t="n"/>
+      <c r="B159" s="34" t="n"/>
+      <c r="C159" s="34" t="n"/>
+      <c r="D159" s="34" t="n"/>
+      <c r="E159" s="34" t="n"/>
+      <c r="F159" s="34" t="n"/>
+      <c r="G159" s="34" t="n"/>
+      <c r="H159" s="34" t="n"/>
     </row>
     <row r="160">
-      <c r="A160" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B160" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.482758620689655+$D$36*0.482758620689655^3),0)</f>
-        <v/>
-      </c>
-      <c r="C160" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.482758620689655+$D$37*0.482758620689655^3),0)</f>
-        <v/>
-      </c>
-      <c r="D160" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.482758620689655+$D$38*0.482758620689655^3),0)</f>
-        <v/>
-      </c>
-      <c r="E160" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.482758620689655+$D$39*0.482758620689655^3),0)</f>
-        <v/>
-      </c>
-      <c r="F160" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.482758620689655+$D$40*0.482758620689655^3),0)</f>
-        <v/>
-      </c>
-      <c r="G160" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.482758620689655+$D$41*0.482758620689655^3),0)</f>
-        <v/>
-      </c>
-      <c r="H160" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.482758620689655+$D$42*0.482758620689655^3),0)</f>
-        <v/>
-      </c>
+      <c r="A160" s="34" t="n"/>
+      <c r="B160" s="34" t="n"/>
+      <c r="C160" s="34" t="n"/>
+      <c r="D160" s="34" t="n"/>
+      <c r="E160" s="34" t="n"/>
+      <c r="F160" s="34" t="n"/>
+      <c r="G160" s="34" t="n"/>
+      <c r="H160" s="34" t="n"/>
     </row>
     <row r="161">
-      <c r="A161" s="16" t="n">
-        <v>16</v>
-      </c>
-      <c r="B161" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.517241379310344+$D$36*0.517241379310344^3),0)</f>
-        <v/>
-      </c>
-      <c r="C161" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.517241379310344+$D$37*0.517241379310344^3),0)</f>
-        <v/>
-      </c>
-      <c r="D161" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.517241379310344+$D$38*0.517241379310344^3),0)</f>
-        <v/>
-      </c>
-      <c r="E161" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.517241379310344+$D$39*0.517241379310344^3),0)</f>
-        <v/>
-      </c>
-      <c r="F161" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.517241379310344+$D$40*0.517241379310344^3),0)</f>
-        <v/>
-      </c>
-      <c r="G161" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.517241379310344+$D$41*0.517241379310344^3),0)</f>
-        <v/>
-      </c>
-      <c r="H161" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.517241379310344+$D$42*0.517241379310344^3),0)</f>
-        <v/>
-      </c>
+      <c r="A161" s="34" t="n"/>
+      <c r="B161" s="34" t="n"/>
+      <c r="C161" s="34" t="n"/>
+      <c r="D161" s="34" t="n"/>
+      <c r="E161" s="34" t="n"/>
+      <c r="F161" s="34" t="n"/>
+      <c r="G161" s="34" t="n"/>
+      <c r="H161" s="34" t="n"/>
     </row>
     <row r="162">
-      <c r="A162" s="16" t="n">
-        <v>17</v>
-      </c>
-      <c r="B162" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.551724137931034+$D$36*0.551724137931034^3),0)</f>
-        <v/>
-      </c>
-      <c r="C162" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.551724137931034+$D$37*0.551724137931034^3),0)</f>
-        <v/>
-      </c>
-      <c r="D162" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.551724137931034+$D$38*0.551724137931034^3),0)</f>
-        <v/>
-      </c>
-      <c r="E162" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.551724137931034+$D$39*0.551724137931034^3),0)</f>
-        <v/>
-      </c>
-      <c r="F162" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.551724137931034+$D$40*0.551724137931034^3),0)</f>
-        <v/>
-      </c>
-      <c r="G162" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.551724137931034+$D$41*0.551724137931034^3),0)</f>
-        <v/>
-      </c>
-      <c r="H162" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.551724137931034+$D$42*0.551724137931034^3),0)</f>
-        <v/>
-      </c>
+      <c r="A162" s="34" t="n"/>
+      <c r="B162" s="34" t="n"/>
+      <c r="C162" s="34" t="n"/>
+      <c r="D162" s="34" t="n"/>
+      <c r="E162" s="34" t="n"/>
+      <c r="F162" s="34" t="n"/>
+      <c r="G162" s="34" t="n"/>
+      <c r="H162" s="34" t="n"/>
     </row>
     <row r="163">
-      <c r="A163" s="16" t="n">
-        <v>18</v>
-      </c>
-      <c r="B163" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.586206896551724+$D$36*0.586206896551724^3),0)</f>
-        <v/>
-      </c>
-      <c r="C163" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.586206896551724+$D$37*0.586206896551724^3),0)</f>
-        <v/>
-      </c>
-      <c r="D163" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.586206896551724+$D$38*0.586206896551724^3),0)</f>
-        <v/>
-      </c>
-      <c r="E163" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.586206896551724+$D$39*0.586206896551724^3),0)</f>
-        <v/>
-      </c>
-      <c r="F163" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.586206896551724+$D$40*0.586206896551724^3),0)</f>
-        <v/>
-      </c>
-      <c r="G163" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.586206896551724+$D$41*0.586206896551724^3),0)</f>
-        <v/>
-      </c>
-      <c r="H163" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.586206896551724+$D$42*0.586206896551724^3),0)</f>
-        <v/>
-      </c>
+      <c r="A163" s="34" t="n"/>
+      <c r="B163" s="34" t="n"/>
+      <c r="C163" s="34" t="n"/>
+      <c r="D163" s="34" t="n"/>
+      <c r="E163" s="34" t="n"/>
+      <c r="F163" s="34" t="n"/>
+      <c r="G163" s="34" t="n"/>
+      <c r="H163" s="34" t="n"/>
     </row>
     <row r="164">
-      <c r="A164" s="16" t="n">
-        <v>19</v>
-      </c>
-      <c r="B164" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.620689655172413+$D$36*0.620689655172413^3),0)</f>
-        <v/>
-      </c>
-      <c r="C164" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.620689655172413+$D$37*0.620689655172413^3),0)</f>
-        <v/>
-      </c>
-      <c r="D164" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.620689655172413+$D$38*0.620689655172413^3),0)</f>
-        <v/>
-      </c>
-      <c r="E164" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.620689655172413+$D$39*0.620689655172413^3),0)</f>
-        <v/>
-      </c>
-      <c r="F164" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.620689655172413+$D$40*0.620689655172413^3),0)</f>
-        <v/>
-      </c>
-      <c r="G164" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.620689655172413+$D$41*0.620689655172413^3),0)</f>
-        <v/>
-      </c>
-      <c r="H164" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.620689655172413+$D$42*0.620689655172413^3),0)</f>
-        <v/>
-      </c>
+      <c r="A164" s="34" t="n"/>
+      <c r="B164" s="34" t="n"/>
+      <c r="C164" s="34" t="n"/>
+      <c r="D164" s="34" t="n"/>
+      <c r="E164" s="34" t="n"/>
+      <c r="F164" s="34" t="n"/>
+      <c r="G164" s="34" t="n"/>
+      <c r="H164" s="34" t="n"/>
     </row>
     <row r="165">
-      <c r="A165" s="16" t="n">
-        <v>20</v>
-      </c>
-      <c r="B165" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.655172413793103+$D$36*0.655172413793103^3),0)</f>
-        <v/>
-      </c>
-      <c r="C165" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.655172413793103+$D$37*0.655172413793103^3),0)</f>
-        <v/>
-      </c>
-      <c r="D165" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.655172413793103+$D$38*0.655172413793103^3),0)</f>
-        <v/>
-      </c>
-      <c r="E165" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.655172413793103+$D$39*0.655172413793103^3),0)</f>
-        <v/>
-      </c>
-      <c r="F165" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.655172413793103+$D$40*0.655172413793103^3),0)</f>
-        <v/>
-      </c>
-      <c r="G165" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.655172413793103+$D$41*0.655172413793103^3),0)</f>
-        <v/>
-      </c>
-      <c r="H165" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.655172413793103+$D$42*0.655172413793103^3),0)</f>
-        <v/>
-      </c>
+      <c r="A165" s="34" t="n"/>
+      <c r="B165" s="34" t="n"/>
+      <c r="C165" s="34" t="n"/>
+      <c r="D165" s="34" t="n"/>
+      <c r="E165" s="34" t="n"/>
+      <c r="F165" s="34" t="n"/>
+      <c r="G165" s="34" t="n"/>
+      <c r="H165" s="34" t="n"/>
     </row>
     <row r="166">
-      <c r="A166" s="16" t="n">
-        <v>21</v>
-      </c>
-      <c r="B166" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.689655172413793+$D$36*0.689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="C166" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.689655172413793+$D$37*0.689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="D166" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.689655172413793+$D$38*0.689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="E166" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.689655172413793+$D$39*0.689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="F166" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.689655172413793+$D$40*0.689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="G166" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.689655172413793+$D$41*0.689655172413793^3),0)</f>
-        <v/>
-      </c>
-      <c r="H166" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.689655172413793+$D$42*0.689655172413793^3),0)</f>
-        <v/>
-      </c>
+      <c r="A166" s="34" t="n"/>
+      <c r="B166" s="34" t="n"/>
+      <c r="C166" s="34" t="n"/>
+      <c r="D166" s="34" t="n"/>
+      <c r="E166" s="34" t="n"/>
+      <c r="F166" s="34" t="n"/>
+      <c r="G166" s="34" t="n"/>
+      <c r="H166" s="34" t="n"/>
     </row>
     <row r="167">
-      <c r="A167" s="16" t="n">
-        <v>22</v>
-      </c>
-      <c r="B167" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.724137931034482+$D$36*0.724137931034482^3),0)</f>
-        <v/>
-      </c>
-      <c r="C167" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.724137931034482+$D$37*0.724137931034482^3),0)</f>
-        <v/>
-      </c>
-      <c r="D167" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.724137931034482+$D$38*0.724137931034482^3),0)</f>
-        <v/>
-      </c>
-      <c r="E167" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.724137931034482+$D$39*0.724137931034482^3),0)</f>
-        <v/>
-      </c>
-      <c r="F167" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.724137931034482+$D$40*0.724137931034482^3),0)</f>
-        <v/>
-      </c>
-      <c r="G167" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.724137931034482+$D$41*0.724137931034482^3),0)</f>
-        <v/>
-      </c>
-      <c r="H167" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.724137931034482+$D$42*0.724137931034482^3),0)</f>
-        <v/>
-      </c>
+      <c r="A167" s="34" t="n"/>
+      <c r="B167" s="34" t="n"/>
+      <c r="C167" s="34" t="n"/>
+      <c r="D167" s="34" t="n"/>
+      <c r="E167" s="34" t="n"/>
+      <c r="F167" s="34" t="n"/>
+      <c r="G167" s="34" t="n"/>
+      <c r="H167" s="34" t="n"/>
     </row>
     <row r="168">
-      <c r="A168" s="16" t="n">
-        <v>23</v>
-      </c>
-      <c r="B168" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.758620689655172+$D$36*0.758620689655172^3),0)</f>
-        <v/>
-      </c>
-      <c r="C168" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.758620689655172+$D$37*0.758620689655172^3),0)</f>
-        <v/>
-      </c>
-      <c r="D168" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.758620689655172+$D$38*0.758620689655172^3),0)</f>
-        <v/>
-      </c>
-      <c r="E168" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.758620689655172+$D$39*0.758620689655172^3),0)</f>
-        <v/>
-      </c>
-      <c r="F168" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.758620689655172+$D$40*0.758620689655172^3),0)</f>
-        <v/>
-      </c>
-      <c r="G168" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.758620689655172+$D$41*0.758620689655172^3),0)</f>
-        <v/>
-      </c>
-      <c r="H168" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.758620689655172+$D$42*0.758620689655172^3),0)</f>
-        <v/>
-      </c>
+      <c r="A168" s="34" t="n"/>
+      <c r="B168" s="34" t="n"/>
+      <c r="C168" s="34" t="n"/>
+      <c r="D168" s="34" t="n"/>
+      <c r="E168" s="34" t="n"/>
+      <c r="F168" s="34" t="n"/>
+      <c r="G168" s="34" t="n"/>
+      <c r="H168" s="34" t="n"/>
     </row>
     <row r="169">
-      <c r="A169" s="16" t="n">
-        <v>24</v>
-      </c>
-      <c r="B169" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.793103448275862+$D$36*0.793103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="C169" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.793103448275862+$D$37*0.793103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="D169" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.793103448275862+$D$38*0.793103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="E169" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.793103448275862+$D$39*0.793103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="F169" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.793103448275862+$D$40*0.793103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="G169" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.793103448275862+$D$41*0.793103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="H169" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.793103448275862+$D$42*0.793103448275862^3),0)</f>
-        <v/>
-      </c>
+      <c r="A169" s="34" t="n"/>
+      <c r="B169" s="34" t="n"/>
+      <c r="C169" s="34" t="n"/>
+      <c r="D169" s="34" t="n"/>
+      <c r="E169" s="34" t="n"/>
+      <c r="F169" s="34" t="n"/>
+      <c r="G169" s="34" t="n"/>
+      <c r="H169" s="34" t="n"/>
     </row>
     <row r="170">
-      <c r="A170" s="16" t="n">
-        <v>25</v>
-      </c>
-      <c r="B170" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.827586206896551+$D$36*0.827586206896551^3),0)</f>
-        <v/>
-      </c>
-      <c r="C170" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.827586206896551+$D$37*0.827586206896551^3),0)</f>
-        <v/>
-      </c>
-      <c r="D170" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.827586206896551+$D$38*0.827586206896551^3),0)</f>
-        <v/>
-      </c>
-      <c r="E170" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.827586206896551+$D$39*0.827586206896551^3),0)</f>
-        <v/>
-      </c>
-      <c r="F170" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.827586206896551+$D$40*0.827586206896551^3),0)</f>
-        <v/>
-      </c>
-      <c r="G170" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.827586206896551+$D$41*0.827586206896551^3),0)</f>
-        <v/>
-      </c>
-      <c r="H170" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.827586206896551+$D$42*0.827586206896551^3),0)</f>
-        <v/>
-      </c>
+      <c r="A170" s="34" t="n"/>
+      <c r="B170" s="34" t="n"/>
+      <c r="C170" s="34" t="n"/>
+      <c r="D170" s="34" t="n"/>
+      <c r="E170" s="34" t="n"/>
+      <c r="F170" s="34" t="n"/>
+      <c r="G170" s="34" t="n"/>
+      <c r="H170" s="34" t="n"/>
     </row>
     <row r="171">
-      <c r="A171" s="16" t="n">
-        <v>26</v>
-      </c>
-      <c r="B171" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.862068965517241+$D$36*0.862068965517241^3),0)</f>
-        <v/>
-      </c>
-      <c r="C171" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.862068965517241+$D$37*0.862068965517241^3),0)</f>
-        <v/>
-      </c>
-      <c r="D171" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.862068965517241+$D$38*0.862068965517241^3),0)</f>
-        <v/>
-      </c>
-      <c r="E171" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.862068965517241+$D$39*0.862068965517241^3),0)</f>
-        <v/>
-      </c>
-      <c r="F171" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.862068965517241+$D$40*0.862068965517241^3),0)</f>
-        <v/>
-      </c>
-      <c r="G171" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.862068965517241+$D$41*0.862068965517241^3),0)</f>
-        <v/>
-      </c>
-      <c r="H171" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.862068965517241+$D$42*0.862068965517241^3),0)</f>
-        <v/>
-      </c>
+      <c r="A171" s="34" t="n"/>
+      <c r="B171" s="34" t="n"/>
+      <c r="C171" s="34" t="n"/>
+      <c r="D171" s="34" t="n"/>
+      <c r="E171" s="34" t="n"/>
+      <c r="F171" s="34" t="n"/>
+      <c r="G171" s="34" t="n"/>
+      <c r="H171" s="34" t="n"/>
     </row>
     <row r="172">
-      <c r="A172" s="16" t="n">
-        <v>27</v>
-      </c>
-      <c r="B172" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.896551724137931+$D$36*0.896551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="C172" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.896551724137931+$D$37*0.896551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="D172" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.896551724137931+$D$38*0.896551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="E172" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.896551724137931+$D$39*0.896551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="F172" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.896551724137931+$D$40*0.896551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="G172" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.896551724137931+$D$41*0.896551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="H172" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.896551724137931+$D$42*0.896551724137931^3),0)</f>
-        <v/>
-      </c>
+      <c r="A172" s="34" t="n"/>
+      <c r="B172" s="34" t="n"/>
+      <c r="C172" s="34" t="n"/>
+      <c r="D172" s="34" t="n"/>
+      <c r="E172" s="34" t="n"/>
+      <c r="F172" s="34" t="n"/>
+      <c r="G172" s="34" t="n"/>
+      <c r="H172" s="34" t="n"/>
     </row>
     <row r="173">
-      <c r="A173" s="16" t="n">
-        <v>28</v>
-      </c>
-      <c r="B173" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.93103448275862+$D$36*0.93103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="C173" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.93103448275862+$D$37*0.93103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="D173" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.93103448275862+$D$38*0.93103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="E173" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.93103448275862+$D$39*0.93103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="F173" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.93103448275862+$D$40*0.93103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="G173" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.93103448275862+$D$41*0.93103448275862^3),0)</f>
-        <v/>
-      </c>
-      <c r="H173" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.93103448275862+$D$42*0.93103448275862^3),0)</f>
-        <v/>
-      </c>
+      <c r="A173" s="34" t="n"/>
+      <c r="B173" s="34" t="n"/>
+      <c r="C173" s="34" t="n"/>
+      <c r="D173" s="34" t="n"/>
+      <c r="E173" s="34" t="n"/>
+      <c r="F173" s="34" t="n"/>
+      <c r="G173" s="34" t="n"/>
+      <c r="H173" s="34" t="n"/>
     </row>
     <row r="174">
-      <c r="A174" s="16" t="n">
-        <v>29</v>
-      </c>
-      <c r="B174" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*0.96551724137931+$D$36*0.96551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="C174" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*0.96551724137931+$D$37*0.96551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="D174" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*0.96551724137931+$D$38*0.96551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="E174" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*0.96551724137931+$D$39*0.96551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="F174" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*0.96551724137931+$D$40*0.96551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="G174" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*0.96551724137931+$D$41*0.96551724137931^3),0)</f>
-        <v/>
-      </c>
-      <c r="H174" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*0.96551724137931+$D$42*0.96551724137931^3),0)</f>
-        <v/>
-      </c>
+      <c r="A174" s="34" t="n"/>
+      <c r="B174" s="34" t="n"/>
+      <c r="C174" s="34" t="n"/>
+      <c r="D174" s="34" t="n"/>
+      <c r="E174" s="34" t="n"/>
+      <c r="F174" s="34" t="n"/>
+      <c r="G174" s="34" t="n"/>
+      <c r="H174" s="34" t="n"/>
     </row>
     <row r="175">
-      <c r="A175" s="16" t="n">
-        <v>30</v>
-      </c>
-      <c r="B175" s="16">
-        <f>ROUND($B$36+($C$36-$B$36)*((1-$D$36)*1+$D$36*1^3),0)</f>
-        <v/>
-      </c>
-      <c r="C175" s="16">
-        <f>ROUND($B$37+($C$37-$B$37)*((1-$D$37)*1+$D$37*1^3),0)</f>
-        <v/>
-      </c>
-      <c r="D175" s="16">
-        <f>ROUND($B$38+($C$38-$B$38)*((1-$D$38)*1+$D$38*1^3),0)</f>
-        <v/>
-      </c>
-      <c r="E175" s="16">
-        <f>ROUND($B$39+($C$39-$B$39)*((1-$D$39)*1+$D$39*1^3),0)</f>
-        <v/>
-      </c>
-      <c r="F175" s="16">
-        <f>ROUND($B$40+($C$40-$B$40)*((1-$D$40)*1+$D$40*1^3),0)</f>
-        <v/>
-      </c>
-      <c r="G175" s="16">
-        <f>ROUND($B$41+($C$41-$B$41)*((1-$D$41)*1+$D$41*1^3),0)</f>
-        <v/>
-      </c>
-      <c r="H175" s="16">
-        <f>ROUND($B$42+($C$42-$B$42)*((1-$D$42)*1+$D$42*1^3),0)</f>
-        <v/>
-      </c>
+      <c r="A175" s="34" t="n"/>
+      <c r="B175" s="34" t="n"/>
+      <c r="C175" s="34" t="n"/>
+      <c r="D175" s="34" t="n"/>
+      <c r="E175" s="34" t="n"/>
+      <c r="F175" s="34" t="n"/>
+      <c r="G175" s="34" t="n"/>
+      <c r="H175" s="34" t="n"/>
     </row>
     <row r="177" ht="26" customHeight="1" s="24">
       <c r="A177" s="27" t="inlineStr">
@@ -4891,9 +5554,9 @@
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="A177:H177"/>
     <mergeCell ref="A11:F11"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A177:Z177"/>
     <mergeCell ref="A3:E3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
